--- a/research/traditional_assets/database/data/singapore/singapore_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_retail_grocery_and_food.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06924579469179407</v>
+        <v>0.06916542684081803</v>
       </c>
       <c r="C2">
-        <v>1870.96525565296</v>
+        <v>1854.347172164259</v>
       </c>
       <c r="D2">
-        <v>1597.96525565296</v>
+        <v>1600.126172164259</v>
       </c>
       <c r="E2">
-        <v>-71.09999999999999</v>
+        <v>-52.321</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18.779</v>
       </c>
       <c r="G2">
         <v>273</v>
@@ -1451,28 +1451,28 @@
         <v>126</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9445836999999999</v>
       </c>
       <c r="N2">
-        <v>126</v>
+        <v>125.0554163</v>
       </c>
       <c r="O2">
-        <v>21.42</v>
+        <v>21.259420771</v>
       </c>
       <c r="P2">
-        <v>104.58</v>
+        <v>103.795995529</v>
       </c>
       <c r="Q2">
-        <v>118.18</v>
+        <v>117.395995529</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06924579469179407</v>
+        <v>0.06944236044527073</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5460129433087928</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>133.3920964335929</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06916542684081803</v>
+        <v>0.06908505898984196</v>
       </c>
       <c r="C3">
-        <v>1854.347172164259</v>
+        <v>1837.734940972176</v>
       </c>
       <c r="D3">
-        <v>1600.126172164259</v>
+        <v>1602.292940972176</v>
       </c>
       <c r="E3">
-        <v>-52.321</v>
+        <v>-33.54199999999999</v>
       </c>
       <c r="F3">
-        <v>18.779</v>
+        <v>37.558</v>
       </c>
       <c r="G3">
         <v>273</v>
@@ -1533,28 +1533,28 @@
         <v>126</v>
       </c>
       <c r="M3">
-        <v>0.9445836999999999</v>
+        <v>1.8891674</v>
       </c>
       <c r="N3">
-        <v>125.0554163</v>
+        <v>124.1108326</v>
       </c>
       <c r="O3">
-        <v>21.259420771</v>
+        <v>21.098841542</v>
       </c>
       <c r="P3">
-        <v>103.795995529</v>
+        <v>103.011991058</v>
       </c>
       <c r="Q3">
-        <v>117.395995529</v>
+        <v>116.611991058</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06944236044527073</v>
+        <v>0.0696429377447367</v>
       </c>
       <c r="T3">
-        <v>0.5460129433087928</v>
+        <v>0.5506452135043119</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>133.3920964335929</v>
+        <v>66.69604821679646</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06908505898984196</v>
+        <v>0.06900469113886593</v>
       </c>
       <c r="C4">
-        <v>1837.734940972176</v>
+        <v>1821.12858588315</v>
       </c>
       <c r="D4">
-        <v>1602.292940972176</v>
+        <v>1604.46558588315</v>
       </c>
       <c r="E4">
-        <v>-33.54199999999999</v>
+        <v>-14.763</v>
       </c>
       <c r="F4">
-        <v>37.558</v>
+        <v>56.337</v>
       </c>
       <c r="G4">
         <v>273</v>
@@ -1615,28 +1615,28 @@
         <v>126</v>
       </c>
       <c r="M4">
-        <v>1.8891674</v>
+        <v>2.8337511</v>
       </c>
       <c r="N4">
-        <v>124.1108326</v>
+        <v>123.1662489</v>
       </c>
       <c r="O4">
-        <v>21.098841542</v>
+        <v>20.938262313</v>
       </c>
       <c r="P4">
-        <v>103.011991058</v>
+        <v>102.227986587</v>
       </c>
       <c r="Q4">
-        <v>116.611991058</v>
+        <v>115.827986587</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0696429377447367</v>
+        <v>0.06984765065862467</v>
       </c>
       <c r="T4">
-        <v>0.5506452135043119</v>
+        <v>0.5553729944255118</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.69604821679646</v>
+        <v>44.46403214453098</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06900469113886593</v>
+        <v>0.06892432328788987</v>
       </c>
       <c r="C5">
-        <v>1821.12858588315</v>
+        <v>1804.528130832915</v>
       </c>
       <c r="D5">
-        <v>1604.46558588315</v>
+        <v>1606.644130832915</v>
       </c>
       <c r="E5">
-        <v>-14.763</v>
+        <v>4.016000000000005</v>
       </c>
       <c r="F5">
-        <v>56.337</v>
+        <v>75.116</v>
       </c>
       <c r="G5">
         <v>273</v>
@@ -1697,28 +1697,28 @@
         <v>126</v>
       </c>
       <c r="M5">
-        <v>2.8337511</v>
+        <v>3.7783348</v>
       </c>
       <c r="N5">
-        <v>123.1662489</v>
+        <v>122.2216652</v>
       </c>
       <c r="O5">
-        <v>20.938262313</v>
+        <v>20.777683084</v>
       </c>
       <c r="P5">
-        <v>102.227986587</v>
+        <v>101.443982116</v>
       </c>
       <c r="Q5">
-        <v>115.827986587</v>
+        <v>115.043982116</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06984765065862467</v>
+        <v>0.07005662842488529</v>
       </c>
       <c r="T5">
-        <v>0.5553729944255118</v>
+        <v>0.56019927078257</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.46403214453098</v>
+        <v>33.34802410839823</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06892432328788987</v>
+        <v>0.06884395543691382</v>
       </c>
       <c r="C6">
-        <v>1804.528130832915</v>
+        <v>1787.933599887385</v>
       </c>
       <c r="D6">
-        <v>1606.644130832915</v>
+        <v>1608.828599887385</v>
       </c>
       <c r="E6">
-        <v>4.016000000000005</v>
+        <v>22.795</v>
       </c>
       <c r="F6">
-        <v>75.116</v>
+        <v>93.895</v>
       </c>
       <c r="G6">
         <v>273</v>
@@ -1779,28 +1779,28 @@
         <v>126</v>
       </c>
       <c r="M6">
-        <v>3.7783348</v>
+        <v>4.7229185</v>
       </c>
       <c r="N6">
-        <v>122.2216652</v>
+        <v>121.2770815</v>
       </c>
       <c r="O6">
-        <v>20.777683084</v>
+        <v>20.617103855</v>
       </c>
       <c r="P6">
-        <v>101.443982116</v>
+        <v>100.659977645</v>
       </c>
       <c r="Q6">
-        <v>115.043982116</v>
+        <v>114.259977645</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07005662842488529</v>
+        <v>0.07027000572306719</v>
       </c>
       <c r="T6">
-        <v>0.56019927078257</v>
+        <v>0.5651271529576716</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.34802410839823</v>
+        <v>26.67841928671858</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06884395543691382</v>
+        <v>0.06876358758593777</v>
       </c>
       <c r="C7">
-        <v>1787.933599887385</v>
+        <v>1771.345017243533</v>
       </c>
       <c r="D7">
-        <v>1608.828599887385</v>
+        <v>1611.019017243533</v>
       </c>
       <c r="E7">
-        <v>22.795</v>
+        <v>41.57400000000001</v>
       </c>
       <c r="F7">
-        <v>93.895</v>
+        <v>112.674</v>
       </c>
       <c r="G7">
         <v>273</v>
@@ -1861,28 +1861,28 @@
         <v>126</v>
       </c>
       <c r="M7">
-        <v>4.7229185</v>
+        <v>5.6675022</v>
       </c>
       <c r="N7">
-        <v>121.2770815</v>
+        <v>120.3324978</v>
       </c>
       <c r="O7">
-        <v>20.617103855</v>
+        <v>20.456524626</v>
       </c>
       <c r="P7">
-        <v>100.659977645</v>
+        <v>99.87597317399999</v>
       </c>
       <c r="Q7">
-        <v>114.259977645</v>
+        <v>113.475973174</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07027000572306719</v>
+        <v>0.07048792296376359</v>
       </c>
       <c r="T7">
-        <v>0.5651271529576716</v>
+        <v>0.5701598836896902</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.67841928671858</v>
+        <v>22.23201607226548</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06876358758593777</v>
+        <v>0.06868321973496173</v>
       </c>
       <c r="C8">
-        <v>1771.345017243533</v>
+        <v>1754.762407230291</v>
       </c>
       <c r="D8">
-        <v>1611.019017243533</v>
+        <v>1613.215407230291</v>
       </c>
       <c r="E8">
-        <v>41.574</v>
+        <v>60.35299999999998</v>
       </c>
       <c r="F8">
-        <v>112.674</v>
+        <v>131.453</v>
       </c>
       <c r="G8">
         <v>273</v>
@@ -1943,28 +1943,28 @@
         <v>126</v>
       </c>
       <c r="M8">
-        <v>5.667502199999999</v>
+        <v>6.612085899999999</v>
       </c>
       <c r="N8">
-        <v>120.3324978</v>
+        <v>119.3879141</v>
       </c>
       <c r="O8">
-        <v>20.456524626</v>
+        <v>20.295945397</v>
       </c>
       <c r="P8">
-        <v>99.87597317399999</v>
+        <v>99.09196870300001</v>
       </c>
       <c r="Q8">
-        <v>113.475973174</v>
+        <v>112.691968703</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07048792296376359</v>
+        <v>0.07071052659673303</v>
       </c>
       <c r="T8">
-        <v>0.5701598836896902</v>
+        <v>0.5753008451901394</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.23201607226549</v>
+        <v>19.05601377622756</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06868321973496172</v>
+        <v>0.06860285188398567</v>
       </c>
       <c r="C9">
-        <v>1754.762407230291</v>
+        <v>1738.185794309448</v>
       </c>
       <c r="D9">
-        <v>1613.215407230291</v>
+        <v>1615.417794309448</v>
       </c>
       <c r="E9">
-        <v>60.35300000000001</v>
+        <v>79.13200000000001</v>
       </c>
       <c r="F9">
-        <v>131.453</v>
+        <v>150.232</v>
       </c>
       <c r="G9">
         <v>273</v>
@@ -2025,28 +2025,28 @@
         <v>126</v>
       </c>
       <c r="M9">
-        <v>6.612085899999999</v>
+        <v>7.556669599999999</v>
       </c>
       <c r="N9">
-        <v>119.3879141</v>
+        <v>118.4433304</v>
       </c>
       <c r="O9">
-        <v>20.295945397</v>
+        <v>20.135366168</v>
       </c>
       <c r="P9">
-        <v>99.09196870300001</v>
+        <v>98.307964232</v>
       </c>
       <c r="Q9">
-        <v>112.691968703</v>
+        <v>111.907964232</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07071052659673303</v>
+        <v>0.07093796943911486</v>
       </c>
       <c r="T9">
-        <v>0.5753008451901394</v>
+        <v>0.5805535667232069</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.05601377622756</v>
+        <v>16.67401205419912</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06860285188398567</v>
+        <v>0.06852248403300963</v>
       </c>
       <c r="C10">
-        <v>1738.185794309448</v>
+        <v>1721.615203076555</v>
       </c>
       <c r="D10">
-        <v>1615.417794309448</v>
+        <v>1617.626203076555</v>
       </c>
       <c r="E10">
-        <v>79.13200000000001</v>
+        <v>97.91099999999997</v>
       </c>
       <c r="F10">
-        <v>150.232</v>
+        <v>169.011</v>
       </c>
       <c r="G10">
         <v>273</v>
@@ -2107,28 +2107,28 @@
         <v>126</v>
       </c>
       <c r="M10">
-        <v>7.556669599999999</v>
+        <v>8.501253299999998</v>
       </c>
       <c r="N10">
-        <v>118.4433304</v>
+        <v>117.4987467</v>
       </c>
       <c r="O10">
-        <v>20.135366168</v>
+        <v>19.974786939</v>
       </c>
       <c r="P10">
-        <v>98.307964232</v>
+        <v>97.523959761</v>
       </c>
       <c r="Q10">
-        <v>111.907964232</v>
+        <v>111.123959761</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07093796943911486</v>
+        <v>0.0711704110252853</v>
       </c>
       <c r="T10">
-        <v>0.5805535667232069</v>
+        <v>0.5859217326855727</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.67401205419912</v>
+        <v>14.82134404817699</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06852248403300963</v>
+        <v>0.06844211618203357</v>
       </c>
       <c r="C11">
-        <v>1721.615203076555</v>
+        <v>1705.050658261849</v>
       </c>
       <c r="D11">
-        <v>1617.626203076555</v>
+        <v>1619.840658261849</v>
       </c>
       <c r="E11">
-        <v>97.91099999999997</v>
+        <v>116.69</v>
       </c>
       <c r="F11">
-        <v>169.011</v>
+        <v>187.79</v>
       </c>
       <c r="G11">
         <v>273</v>
@@ -2189,28 +2189,28 @@
         <v>126</v>
       </c>
       <c r="M11">
-        <v>8.501253299999998</v>
+        <v>9.445836999999997</v>
       </c>
       <c r="N11">
-        <v>117.4987467</v>
+        <v>116.554163</v>
       </c>
       <c r="O11">
-        <v>19.974786939</v>
+        <v>19.81420771</v>
       </c>
       <c r="P11">
-        <v>97.523959761</v>
+        <v>96.73995529</v>
       </c>
       <c r="Q11">
-        <v>111.123959761</v>
+        <v>110.33995529</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0711704110252853</v>
+        <v>0.07140801798003731</v>
       </c>
       <c r="T11">
-        <v>0.5859217326855727</v>
+        <v>0.5914091912248799</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.82134404817699</v>
+        <v>13.3392096433593</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06844211618203357</v>
+        <v>0.06849869833105753</v>
       </c>
       <c r="C12">
-        <v>1705.050658261849</v>
+        <v>1684.711963080269</v>
       </c>
       <c r="D12">
-        <v>1619.840658261849</v>
+        <v>1618.280963080269</v>
       </c>
       <c r="E12">
-        <v>116.69</v>
+        <v>135.469</v>
       </c>
       <c r="F12">
-        <v>187.79</v>
+        <v>206.569</v>
       </c>
       <c r="G12">
         <v>273</v>
@@ -2271,45 +2271,45 @@
         <v>126</v>
       </c>
       <c r="M12">
-        <v>9.445836999999999</v>
+        <v>10.7002742</v>
       </c>
       <c r="N12">
-        <v>116.554163</v>
+        <v>115.2997258</v>
       </c>
       <c r="O12">
-        <v>19.81420771</v>
+        <v>19.600953386</v>
       </c>
       <c r="P12">
-        <v>96.73995529</v>
+        <v>95.698772414</v>
       </c>
       <c r="Q12">
-        <v>110.33995529</v>
+        <v>109.298772414</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07140801798003731</v>
+        <v>0.07165096441691857</v>
       </c>
       <c r="T12">
-        <v>0.5914091912248799</v>
+        <v>0.5970199634392278</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.17</v>
       </c>
       <c r="W12">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.33920964335929</v>
+        <v>11.77539917621924</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06849869833105753</v>
+        <v>0.06843078048008147</v>
       </c>
       <c r="C13">
-        <v>1684.711963080269</v>
+        <v>1667.805490099795</v>
       </c>
       <c r="D13">
-        <v>1618.280963080269</v>
+        <v>1620.153490099795</v>
       </c>
       <c r="E13">
-        <v>135.469</v>
+        <v>154.248</v>
       </c>
       <c r="F13">
-        <v>206.569</v>
+        <v>225.348</v>
       </c>
       <c r="G13">
         <v>273</v>
@@ -2353,28 +2353,28 @@
         <v>126</v>
       </c>
       <c r="M13">
-        <v>10.7002742</v>
+        <v>11.6730264</v>
       </c>
       <c r="N13">
-        <v>115.2997258</v>
+        <v>114.3269736</v>
       </c>
       <c r="O13">
-        <v>19.600953386</v>
+        <v>19.435585512</v>
       </c>
       <c r="P13">
-        <v>95.698772414</v>
+        <v>94.891388088</v>
       </c>
       <c r="Q13">
-        <v>109.298772414</v>
+        <v>108.491388088</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07165096441691857</v>
+        <v>0.07189943236372895</v>
       </c>
       <c r="T13">
-        <v>0.5970199634392278</v>
+        <v>0.6027582532039018</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.77539917621924</v>
+        <v>10.79411591153431</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06843078048008147</v>
+        <v>0.06836286262910543</v>
       </c>
       <c r="C14">
-        <v>1667.805490099795</v>
+        <v>1650.903355574083</v>
       </c>
       <c r="D14">
-        <v>1620.153490099795</v>
+        <v>1622.030355574082</v>
       </c>
       <c r="E14">
-        <v>154.248</v>
+        <v>173.027</v>
       </c>
       <c r="F14">
-        <v>225.348</v>
+        <v>244.127</v>
       </c>
       <c r="G14">
         <v>273</v>
@@ -2435,28 +2435,28 @@
         <v>126</v>
       </c>
       <c r="M14">
-        <v>11.6730264</v>
+        <v>12.6457786</v>
       </c>
       <c r="N14">
-        <v>114.3269736</v>
+        <v>113.3542214</v>
       </c>
       <c r="O14">
-        <v>19.435585512</v>
+        <v>19.270217638</v>
       </c>
       <c r="P14">
-        <v>94.891388088</v>
+        <v>94.08400376199999</v>
       </c>
       <c r="Q14">
-        <v>108.491388088</v>
+        <v>107.684003762</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07189943236372895</v>
+        <v>0.07215361221736255</v>
       </c>
       <c r="T14">
-        <v>0.6027582532039018</v>
+        <v>0.6086284576758095</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.79411591153431</v>
+        <v>9.963799302954744</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06836286262910543</v>
+        <v>0.06849248477812937</v>
       </c>
       <c r="C15">
-        <v>1650.903355574083</v>
+        <v>1628.546093749029</v>
       </c>
       <c r="D15">
-        <v>1622.030355574082</v>
+        <v>1618.452093749029</v>
       </c>
       <c r="E15">
-        <v>173.027</v>
+        <v>191.806</v>
       </c>
       <c r="F15">
-        <v>244.127</v>
+        <v>262.906</v>
       </c>
       <c r="G15">
         <v>273</v>
@@ -2517,45 +2517,45 @@
         <v>126</v>
       </c>
       <c r="M15">
-        <v>12.6457786</v>
+        <v>14.065471</v>
       </c>
       <c r="N15">
-        <v>113.3542214</v>
+        <v>111.934529</v>
       </c>
       <c r="O15">
-        <v>19.270217638</v>
+        <v>19.02886993</v>
       </c>
       <c r="P15">
-        <v>94.08400376199999</v>
+        <v>92.90565907</v>
       </c>
       <c r="Q15">
-        <v>107.684003762</v>
+        <v>106.50565907</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07215361221736255</v>
+        <v>0.07241370323038299</v>
       </c>
       <c r="T15">
-        <v>0.6086284576758095</v>
+        <v>0.614635178530785</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.17</v>
       </c>
       <c r="W15">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.963799302954744</v>
+        <v>8.95810741069389</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06849248477812937</v>
+        <v>0.06843867692715333</v>
       </c>
       <c r="C16">
-        <v>1628.546093749029</v>
+        <v>1611.250558754687</v>
       </c>
       <c r="D16">
-        <v>1618.452093749029</v>
+        <v>1619.935558754687</v>
       </c>
       <c r="E16">
-        <v>191.806</v>
+        <v>210.585</v>
       </c>
       <c r="F16">
-        <v>262.906</v>
+        <v>281.685</v>
       </c>
       <c r="G16">
         <v>273</v>
@@ -2599,28 +2599,28 @@
         <v>126</v>
       </c>
       <c r="M16">
-        <v>14.065471</v>
+        <v>15.0701475</v>
       </c>
       <c r="N16">
-        <v>111.934529</v>
+        <v>110.9298525</v>
       </c>
       <c r="O16">
-        <v>19.02886993</v>
+        <v>18.858074925</v>
       </c>
       <c r="P16">
-        <v>92.90565907</v>
+        <v>92.071777575</v>
       </c>
       <c r="Q16">
-        <v>106.50565907</v>
+        <v>105.671777575</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07241370323038299</v>
+        <v>0.0726799140319451</v>
       </c>
       <c r="T16">
-        <v>0.614635178530785</v>
+        <v>0.6207832339941128</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.95810741069389</v>
+        <v>8.360900249980965</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06843867692715333</v>
+        <v>0.06838486907617727</v>
       </c>
       <c r="C17">
-        <v>1611.250558754687</v>
+        <v>1593.957745728334</v>
       </c>
       <c r="D17">
-        <v>1619.935558754687</v>
+        <v>1621.421745728334</v>
       </c>
       <c r="E17">
-        <v>210.585</v>
+        <v>229.364</v>
       </c>
       <c r="F17">
-        <v>281.6849999999999</v>
+        <v>300.464</v>
       </c>
       <c r="G17">
         <v>273</v>
@@ -2681,28 +2681,28 @@
         <v>126</v>
       </c>
       <c r="M17">
-        <v>15.0701475</v>
+        <v>16.074824</v>
       </c>
       <c r="N17">
-        <v>110.9298525</v>
+        <v>109.925176</v>
       </c>
       <c r="O17">
-        <v>18.858074925</v>
+        <v>18.68727992</v>
       </c>
       <c r="P17">
-        <v>92.071777575</v>
+        <v>91.23789607999998</v>
       </c>
       <c r="Q17">
-        <v>105.671777575</v>
+        <v>104.83789608</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0726799140319451</v>
+        <v>0.07295246318592533</v>
       </c>
       <c r="T17">
-        <v>0.6207832339941128</v>
+        <v>0.627077671730377</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.360900249980965</v>
+        <v>7.838343984357153</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06838486907617727</v>
+        <v>0.06844394122520123</v>
       </c>
       <c r="C18">
-        <v>1593.957745728334</v>
+        <v>1573.547303760084</v>
       </c>
       <c r="D18">
-        <v>1621.421745728334</v>
+        <v>1619.790303760084</v>
       </c>
       <c r="E18">
-        <v>229.364</v>
+        <v>248.143</v>
       </c>
       <c r="F18">
-        <v>300.464</v>
+        <v>319.243</v>
       </c>
       <c r="G18">
         <v>273</v>
@@ -2763,45 +2763,45 @@
         <v>126</v>
       </c>
       <c r="M18">
-        <v>16.074824</v>
+        <v>17.3348949</v>
       </c>
       <c r="N18">
-        <v>109.925176</v>
+        <v>108.6651051</v>
       </c>
       <c r="O18">
-        <v>18.68727992</v>
+        <v>18.473067867</v>
       </c>
       <c r="P18">
-        <v>91.23789607999998</v>
+        <v>90.19203723300001</v>
       </c>
       <c r="Q18">
-        <v>104.83789608</v>
+        <v>103.792037233</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07295246318592533</v>
+        <v>0.07323157978939906</v>
       </c>
       <c r="T18">
-        <v>0.627077671730377</v>
+        <v>0.6335237826651053</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.17</v>
       </c>
       <c r="W18">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.838343984357153</v>
+        <v>7.268575940428691</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06844394122520123</v>
+        <v>0.06839677337422517</v>
       </c>
       <c r="C19">
-        <v>1573.547303760084</v>
+        <v>1556.070711021958</v>
       </c>
       <c r="D19">
-        <v>1619.790303760084</v>
+        <v>1621.092711021958</v>
       </c>
       <c r="E19">
-        <v>248.143</v>
+        <v>266.922</v>
       </c>
       <c r="F19">
-        <v>319.243</v>
+        <v>338.022</v>
       </c>
       <c r="G19">
         <v>273</v>
@@ -2845,28 +2845,28 @@
         <v>126</v>
       </c>
       <c r="M19">
-        <v>17.3348949</v>
+        <v>18.3545946</v>
       </c>
       <c r="N19">
-        <v>108.6651051</v>
+        <v>107.6454054</v>
       </c>
       <c r="O19">
-        <v>18.473067867</v>
+        <v>18.299718918</v>
       </c>
       <c r="P19">
-        <v>90.19203723300001</v>
+        <v>89.345686482</v>
       </c>
       <c r="Q19">
-        <v>103.792037233</v>
+        <v>102.945686482</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07323157978939906</v>
+        <v>0.07351750411490875</v>
       </c>
       <c r="T19">
-        <v>0.6335237826651053</v>
+        <v>0.6401271158177539</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.268575940428691</v>
+        <v>6.86476616596043</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06839677337422517</v>
+        <v>0.06834960552324913</v>
       </c>
       <c r="C20">
-        <v>1556.070711021958</v>
+        <v>1538.596214394257</v>
       </c>
       <c r="D20">
-        <v>1621.092711021958</v>
+        <v>1622.397214394257</v>
       </c>
       <c r="E20">
-        <v>266.9219999999999</v>
+        <v>285.701</v>
       </c>
       <c r="F20">
-        <v>338.0219999999999</v>
+        <v>356.801</v>
       </c>
       <c r="G20">
         <v>273</v>
@@ -2927,28 +2927,28 @@
         <v>126</v>
       </c>
       <c r="M20">
-        <v>18.3545946</v>
+        <v>19.3742943</v>
       </c>
       <c r="N20">
-        <v>107.6454054</v>
+        <v>106.6257057</v>
       </c>
       <c r="O20">
-        <v>18.299718918</v>
+        <v>18.126369969</v>
       </c>
       <c r="P20">
-        <v>89.345686482</v>
+        <v>88.499335731</v>
       </c>
       <c r="Q20">
-        <v>102.945686482</v>
+        <v>102.099335731</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07351750411490875</v>
+        <v>0.07381048830030756</v>
       </c>
       <c r="T20">
-        <v>0.6401271158177539</v>
+        <v>0.6468934942334309</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.864766165960431</v>
+        <v>6.50346268354146</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06834960552324913</v>
+        <v>0.06830243767227308</v>
       </c>
       <c r="C21">
-        <v>1538.596214394257</v>
+        <v>1521.123818941316</v>
       </c>
       <c r="D21">
-        <v>1622.397214394257</v>
+        <v>1623.703818941316</v>
       </c>
       <c r="E21">
-        <v>285.701</v>
+        <v>304.48</v>
       </c>
       <c r="F21">
-        <v>356.801</v>
+        <v>375.58</v>
       </c>
       <c r="G21">
         <v>273</v>
@@ -3009,28 +3009,28 @@
         <v>126</v>
       </c>
       <c r="M21">
-        <v>19.3742943</v>
+        <v>20.393994</v>
       </c>
       <c r="N21">
-        <v>106.6257057</v>
+        <v>105.606006</v>
       </c>
       <c r="O21">
-        <v>18.126369969</v>
+        <v>17.95302102</v>
       </c>
       <c r="P21">
-        <v>88.499335731</v>
+        <v>87.65298498000001</v>
       </c>
       <c r="Q21">
-        <v>102.099335731</v>
+        <v>101.25298498</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07381048830030756</v>
+        <v>0.07411079709034134</v>
       </c>
       <c r="T21">
-        <v>0.6468934942334309</v>
+        <v>0.6538290321094997</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.50346268354146</v>
+        <v>6.178289549364387</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06830243767227308</v>
+        <v>0.06842956982129703</v>
       </c>
       <c r="C22">
-        <v>1521.123818941316</v>
+        <v>1498.827907842285</v>
       </c>
       <c r="D22">
-        <v>1623.703818941316</v>
+        <v>1620.186907842285</v>
       </c>
       <c r="E22">
-        <v>304.48</v>
+        <v>323.259</v>
       </c>
       <c r="F22">
-        <v>375.58</v>
+        <v>394.359</v>
       </c>
       <c r="G22">
         <v>273</v>
@@ -3091,45 +3091,45 @@
         <v>126</v>
       </c>
       <c r="M22">
-        <v>20.393994</v>
+        <v>21.8080527</v>
       </c>
       <c r="N22">
-        <v>105.606006</v>
+        <v>104.1919473</v>
       </c>
       <c r="O22">
-        <v>17.95302102</v>
+        <v>17.712631041</v>
       </c>
       <c r="P22">
-        <v>87.65298498000001</v>
+        <v>86.479316259</v>
       </c>
       <c r="Q22">
-        <v>101.25298498</v>
+        <v>100.079316259</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07411079709034134</v>
+        <v>0.07441870863455319</v>
       </c>
       <c r="T22">
-        <v>0.6538290321094997</v>
+        <v>0.6609401532229374</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.17</v>
       </c>
       <c r="W22">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.178289549364387</v>
+        <v>5.777682296228126</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06842956982129701</v>
+        <v>0.06839070197032097</v>
       </c>
       <c r="C23">
-        <v>1498.827907842285</v>
+        <v>1481.12250789136</v>
       </c>
       <c r="D23">
-        <v>1620.186907842285</v>
+        <v>1621.26050789136</v>
       </c>
       <c r="E23">
-        <v>323.259</v>
+        <v>342.038</v>
       </c>
       <c r="F23">
-        <v>394.359</v>
+        <v>413.138</v>
       </c>
       <c r="G23">
         <v>273</v>
@@ -3173,28 +3173,28 @@
         <v>126</v>
       </c>
       <c r="M23">
-        <v>21.8080527</v>
+        <v>22.8465314</v>
       </c>
       <c r="N23">
-        <v>104.1919473</v>
+        <v>103.1534686</v>
       </c>
       <c r="O23">
-        <v>17.712631041</v>
+        <v>17.536089662</v>
       </c>
       <c r="P23">
-        <v>86.479316259</v>
+        <v>85.617378938</v>
       </c>
       <c r="Q23">
-        <v>100.079316259</v>
+        <v>99.217378938</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07441870863455319</v>
+        <v>0.07473451534656535</v>
       </c>
       <c r="T23">
-        <v>0.6609401532229374</v>
+        <v>0.6682336107751812</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.777682296228126</v>
+        <v>5.515060373672303</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06839070197032097</v>
+        <v>0.06835183411934492</v>
       </c>
       <c r="C24">
-        <v>1481.12250789136</v>
+        <v>1463.418531703749</v>
       </c>
       <c r="D24">
-        <v>1621.26050789136</v>
+        <v>1622.335531703749</v>
       </c>
       <c r="E24">
-        <v>342.038</v>
+        <v>360.817</v>
       </c>
       <c r="F24">
-        <v>413.138</v>
+        <v>431.917</v>
       </c>
       <c r="G24">
         <v>273</v>
@@ -3255,28 +3255,28 @@
         <v>126</v>
       </c>
       <c r="M24">
-        <v>22.8465314</v>
+        <v>23.8850101</v>
       </c>
       <c r="N24">
-        <v>103.1534686</v>
+        <v>102.1149899</v>
       </c>
       <c r="O24">
-        <v>17.536089662</v>
+        <v>17.359548283</v>
       </c>
       <c r="P24">
-        <v>85.617378938</v>
+        <v>84.755441617</v>
       </c>
       <c r="Q24">
-        <v>99.217378938</v>
+        <v>98.355441617</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07473451534656535</v>
+        <v>0.07505852483031808</v>
       </c>
       <c r="T24">
-        <v>0.6682336107751812</v>
+        <v>0.6757165087833275</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.515060373672303</v>
+        <v>5.275275140034377</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06835183411934492</v>
+        <v>0.06831296626836889</v>
       </c>
       <c r="C25">
-        <v>1463.418531703749</v>
+        <v>1445.715982113535</v>
       </c>
       <c r="D25">
-        <v>1622.335531703749</v>
+        <v>1623.411982113535</v>
       </c>
       <c r="E25">
-        <v>360.817</v>
+        <v>379.596</v>
       </c>
       <c r="F25">
-        <v>431.917</v>
+        <v>450.696</v>
       </c>
       <c r="G25">
         <v>273</v>
@@ -3337,28 +3337,28 @@
         <v>126</v>
       </c>
       <c r="M25">
-        <v>23.8850101</v>
+        <v>24.9234888</v>
       </c>
       <c r="N25">
-        <v>102.1149899</v>
+        <v>101.0765112</v>
       </c>
       <c r="O25">
-        <v>17.359548283</v>
+        <v>17.183006904</v>
       </c>
       <c r="P25">
-        <v>84.755441617</v>
+        <v>83.893504296</v>
       </c>
       <c r="Q25">
-        <v>98.355441617</v>
+        <v>97.493504296</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07505852483031808</v>
+        <v>0.07539106087943273</v>
       </c>
       <c r="T25">
-        <v>0.6757165087833275</v>
+        <v>0.6833963251601091</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.275275140034377</v>
+        <v>5.055472009199611</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06831296626836889</v>
+        <v>0.06827409841739283</v>
       </c>
       <c r="C26">
-        <v>1445.715982113535</v>
+        <v>1428.014861962328</v>
       </c>
       <c r="D26">
-        <v>1623.411982113535</v>
+        <v>1624.489861962327</v>
       </c>
       <c r="E26">
-        <v>379.596</v>
+        <v>398.375</v>
       </c>
       <c r="F26">
-        <v>450.696</v>
+        <v>469.475</v>
       </c>
       <c r="G26">
         <v>273</v>
@@ -3419,28 +3419,28 @@
         <v>126</v>
       </c>
       <c r="M26">
-        <v>24.9234888</v>
+        <v>25.9619675</v>
       </c>
       <c r="N26">
-        <v>101.0765112</v>
+        <v>100.0380325</v>
       </c>
       <c r="O26">
-        <v>17.183006904</v>
+        <v>17.006465525</v>
       </c>
       <c r="P26">
-        <v>83.893504296</v>
+        <v>83.031566975</v>
       </c>
       <c r="Q26">
-        <v>97.493504296</v>
+        <v>96.631566975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07539106087943273</v>
+        <v>0.07573246455652377</v>
       </c>
       <c r="T26">
-        <v>0.6833963251601091</v>
+        <v>0.6912809366402716</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.055472009199612</v>
+        <v>4.853253128831627</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06827409841739283</v>
+        <v>0.06823523056641677</v>
       </c>
       <c r="C27">
-        <v>1428.014861962328</v>
+        <v>1410.315174099287</v>
       </c>
       <c r="D27">
-        <v>1624.489861962327</v>
+        <v>1625.569174099287</v>
       </c>
       <c r="E27">
-        <v>398.375</v>
+        <v>417.154</v>
       </c>
       <c r="F27">
-        <v>469.475</v>
+        <v>488.254</v>
       </c>
       <c r="G27">
         <v>273</v>
@@ -3501,28 +3501,28 @@
         <v>126</v>
       </c>
       <c r="M27">
-        <v>25.9619675</v>
+        <v>27.0004462</v>
       </c>
       <c r="N27">
-        <v>100.0380325</v>
+        <v>98.9995538</v>
       </c>
       <c r="O27">
-        <v>17.006465525</v>
+        <v>16.829924146</v>
       </c>
       <c r="P27">
-        <v>83.031566975</v>
+        <v>82.169629654</v>
       </c>
       <c r="Q27">
-        <v>96.631566975</v>
+        <v>95.769629654</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07573246455652377</v>
+        <v>0.07608309536002267</v>
       </c>
       <c r="T27">
-        <v>0.6912809366402716</v>
+        <v>0.6993786457280061</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.853253128831627</v>
+        <v>4.666589546953487</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06823523056641677</v>
+        <v>0.06875661271544073</v>
       </c>
       <c r="C28">
-        <v>1410.315174099287</v>
+        <v>1377.176397923351</v>
       </c>
       <c r="D28">
-        <v>1625.569174099287</v>
+        <v>1611.209397923352</v>
       </c>
       <c r="E28">
-        <v>417.154</v>
+        <v>435.933</v>
       </c>
       <c r="F28">
-        <v>488.254</v>
+        <v>507.033</v>
       </c>
       <c r="G28">
         <v>273</v>
@@ -3583,45 +3583,45 @@
         <v>126</v>
       </c>
       <c r="M28">
-        <v>27.0004462</v>
+        <v>29.3065074</v>
       </c>
       <c r="N28">
-        <v>98.9995538</v>
+        <v>96.6934926</v>
       </c>
       <c r="O28">
-        <v>16.829924146</v>
+        <v>16.437893742</v>
       </c>
       <c r="P28">
-        <v>82.169629654</v>
+        <v>80.255598858</v>
       </c>
       <c r="Q28">
-        <v>95.769629654</v>
+        <v>93.85559885799999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07608309536002267</v>
+        <v>0.0764433324869051</v>
       </c>
       <c r="T28">
-        <v>0.6993786457280061</v>
+        <v>0.7076982098592401</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.17</v>
       </c>
       <c r="W28">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.666589546953487</v>
+        <v>4.299386422279715</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06875661271544073</v>
+        <v>0.06873849486446468</v>
       </c>
       <c r="C29">
-        <v>1377.176397923351</v>
+        <v>1358.892139105187</v>
       </c>
       <c r="D29">
-        <v>1611.209397923352</v>
+        <v>1611.704139105187</v>
       </c>
       <c r="E29">
-        <v>435.933</v>
+        <v>454.712</v>
       </c>
       <c r="F29">
-        <v>507.033</v>
+        <v>525.812</v>
       </c>
       <c r="G29">
         <v>273</v>
@@ -3665,28 +3665,28 @@
         <v>126</v>
       </c>
       <c r="M29">
-        <v>29.3065074</v>
+        <v>30.3919336</v>
       </c>
       <c r="N29">
-        <v>96.6934926</v>
+        <v>95.6080664</v>
       </c>
       <c r="O29">
-        <v>16.437893742</v>
+        <v>16.253371288</v>
       </c>
       <c r="P29">
-        <v>80.255598858</v>
+        <v>79.354695112</v>
       </c>
       <c r="Q29">
-        <v>93.85559885799999</v>
+        <v>92.954695112</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0764433324869051</v>
+        <v>0.07681357620064538</v>
       </c>
       <c r="T29">
-        <v>0.7076982098592401</v>
+        <v>0.7162488729941197</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.299386422279715</v>
+        <v>4.145836907198296</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06873849486446468</v>
+        <v>0.06872037701348863</v>
       </c>
       <c r="C30">
-        <v>1358.892139105187</v>
+        <v>1340.608184212782</v>
       </c>
       <c r="D30">
-        <v>1611.704139105187</v>
+        <v>1612.199184212782</v>
       </c>
       <c r="E30">
-        <v>454.712</v>
+        <v>473.491</v>
       </c>
       <c r="F30">
-        <v>525.812</v>
+        <v>544.591</v>
       </c>
       <c r="G30">
         <v>273</v>
@@ -3747,28 +3747,28 @@
         <v>126</v>
       </c>
       <c r="M30">
-        <v>30.3919336</v>
+        <v>31.4773598</v>
       </c>
       <c r="N30">
-        <v>95.6080664</v>
+        <v>94.5226402</v>
       </c>
       <c r="O30">
-        <v>16.253371288</v>
+        <v>16.068848834</v>
       </c>
       <c r="P30">
-        <v>79.354695112</v>
+        <v>78.45379136599999</v>
       </c>
       <c r="Q30">
-        <v>92.954695112</v>
+        <v>92.05379136599998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07681357620064538</v>
+        <v>0.07719424931477271</v>
       </c>
       <c r="T30">
-        <v>0.7162488729941197</v>
+        <v>0.7250403998792774</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.145836907198296</v>
+        <v>4.002877013846631</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06872037701348861</v>
+        <v>0.06957375916251257</v>
       </c>
       <c r="C31">
-        <v>1340.608184212782</v>
+        <v>1298.837179442578</v>
       </c>
       <c r="D31">
-        <v>1612.199184212782</v>
+        <v>1589.207179442578</v>
       </c>
       <c r="E31">
-        <v>473.4909999999999</v>
+        <v>492.2699999999999</v>
       </c>
       <c r="F31">
-        <v>544.5909999999999</v>
+        <v>563.3699999999999</v>
       </c>
       <c r="G31">
         <v>273</v>
@@ -3829,45 +3829,45 @@
         <v>126</v>
       </c>
       <c r="M31">
-        <v>31.4773598</v>
+        <v>34.534581</v>
       </c>
       <c r="N31">
-        <v>94.52264020000001</v>
+        <v>91.465419</v>
       </c>
       <c r="O31">
-        <v>16.068848834</v>
+        <v>15.54912123</v>
       </c>
       <c r="P31">
-        <v>78.453791366</v>
+        <v>75.91629777</v>
       </c>
       <c r="Q31">
-        <v>92.053791366</v>
+        <v>89.51629776999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0771942493147727</v>
+        <v>0.07758579880358939</v>
       </c>
       <c r="T31">
-        <v>0.7250403998792773</v>
+        <v>0.734083113246868</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.17</v>
       </c>
       <c r="W31">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.002877013846632</v>
+        <v>3.648516830130356</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06957375916251257</v>
+        <v>0.06958469131153652</v>
       </c>
       <c r="C32">
-        <v>1298.837179442578</v>
+        <v>1279.767896633999</v>
       </c>
       <c r="D32">
-        <v>1589.207179442578</v>
+        <v>1588.916896633999</v>
       </c>
       <c r="E32">
-        <v>492.2699999999999</v>
+        <v>511.049</v>
       </c>
       <c r="F32">
-        <v>563.3699999999999</v>
+        <v>582.149</v>
       </c>
       <c r="G32">
         <v>273</v>
@@ -3911,28 +3911,28 @@
         <v>126</v>
       </c>
       <c r="M32">
-        <v>34.534581</v>
+        <v>35.6857337</v>
       </c>
       <c r="N32">
-        <v>91.465419</v>
+        <v>90.3142663</v>
       </c>
       <c r="O32">
-        <v>15.54912123</v>
+        <v>15.353425271</v>
       </c>
       <c r="P32">
-        <v>75.91629777</v>
+        <v>74.96084102899999</v>
       </c>
       <c r="Q32">
-        <v>89.51629776999999</v>
+        <v>88.56084102899999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07758579880358939</v>
+        <v>0.07798869755295149</v>
       </c>
       <c r="T32">
-        <v>0.734083113246868</v>
+        <v>0.7433879342483021</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.648516830130356</v>
+        <v>3.530822738835828</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06958469131153652</v>
+        <v>0.07033930346056047</v>
       </c>
       <c r="C33">
-        <v>1279.767896633999</v>
+        <v>1241.204686464061</v>
       </c>
       <c r="D33">
-        <v>1588.916896633999</v>
+        <v>1569.132686464061</v>
       </c>
       <c r="E33">
-        <v>511.049</v>
+        <v>529.828</v>
       </c>
       <c r="F33">
-        <v>582.149</v>
+        <v>600.928</v>
       </c>
       <c r="G33">
         <v>273</v>
@@ -3993,45 +3993,45 @@
         <v>126</v>
       </c>
       <c r="M33">
-        <v>35.6857337</v>
+        <v>38.5194848</v>
       </c>
       <c r="N33">
-        <v>90.3142663</v>
+        <v>87.4805152</v>
       </c>
       <c r="O33">
-        <v>15.353425271</v>
+        <v>14.871687584</v>
       </c>
       <c r="P33">
-        <v>74.96084102899999</v>
+        <v>72.608827616</v>
       </c>
       <c r="Q33">
-        <v>88.56084102899999</v>
+        <v>86.20882761599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07798869755295149</v>
+        <v>0.07840344626553011</v>
       </c>
       <c r="T33">
-        <v>0.7433879342483021</v>
+        <v>0.7529664264556607</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.17</v>
       </c>
       <c r="W33">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.530822738835828</v>
+        <v>3.271071787543742</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07033930346056047</v>
+        <v>0.07037347560958443</v>
       </c>
       <c r="C34">
-        <v>1241.204686464061</v>
+        <v>1221.541424606522</v>
       </c>
       <c r="D34">
-        <v>1569.132686464061</v>
+        <v>1568.248424606522</v>
       </c>
       <c r="E34">
-        <v>529.828</v>
+        <v>548.607</v>
       </c>
       <c r="F34">
-        <v>600.928</v>
+        <v>619.707</v>
       </c>
       <c r="G34">
         <v>273</v>
@@ -4075,28 +4075,28 @@
         <v>126</v>
       </c>
       <c r="M34">
-        <v>38.5194848</v>
+        <v>39.7232187</v>
       </c>
       <c r="N34">
-        <v>87.4805152</v>
+        <v>86.2767813</v>
       </c>
       <c r="O34">
-        <v>14.871687584</v>
+        <v>14.667052821</v>
       </c>
       <c r="P34">
-        <v>72.608827616</v>
+        <v>71.609728479</v>
       </c>
       <c r="Q34">
-        <v>86.20882761599999</v>
+        <v>85.20972847899999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07840344626553011</v>
+        <v>0.07883057553669318</v>
       </c>
       <c r="T34">
-        <v>0.7529664264556607</v>
+        <v>0.7628308438035375</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.271071787543742</v>
+        <v>3.171948400042416</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07037347560958443</v>
+        <v>0.07040764775860837</v>
       </c>
       <c r="C35">
-        <v>1221.541424606522</v>
+        <v>1201.879158813433</v>
       </c>
       <c r="D35">
-        <v>1568.248424606522</v>
+        <v>1567.365158813433</v>
       </c>
       <c r="E35">
-        <v>548.607</v>
+        <v>567.386</v>
       </c>
       <c r="F35">
-        <v>619.707</v>
+        <v>638.486</v>
       </c>
       <c r="G35">
         <v>273</v>
@@ -4157,28 +4157,28 @@
         <v>126</v>
       </c>
       <c r="M35">
-        <v>39.7232187</v>
+        <v>40.9269526</v>
       </c>
       <c r="N35">
-        <v>86.2767813</v>
+        <v>85.07304740000001</v>
       </c>
       <c r="O35">
-        <v>14.667052821</v>
+        <v>14.462418058</v>
       </c>
       <c r="P35">
-        <v>71.609728479</v>
+        <v>70.61062934200001</v>
       </c>
       <c r="Q35">
-        <v>85.20972847899999</v>
+        <v>84.210629342</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07883057553669318</v>
+        <v>0.0792706481191036</v>
       </c>
       <c r="T35">
-        <v>0.7628308438035375</v>
+        <v>0.7729941828892286</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.171948400042416</v>
+        <v>3.078655800041169</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07040764775860837</v>
+        <v>0.07270771990763232</v>
       </c>
       <c r="C36">
-        <v>1201.879158813433</v>
+        <v>1125.852661417825</v>
       </c>
       <c r="D36">
-        <v>1567.365158813433</v>
+        <v>1510.117661417825</v>
       </c>
       <c r="E36">
-        <v>567.386</v>
+        <v>586.165</v>
       </c>
       <c r="F36">
-        <v>638.486</v>
+        <v>657.265</v>
       </c>
       <c r="G36">
         <v>273</v>
@@ -4239,45 +4239,45 @@
         <v>126</v>
       </c>
       <c r="M36">
-        <v>40.9269526</v>
+        <v>47.2573535</v>
       </c>
       <c r="N36">
-        <v>85.07304740000001</v>
+        <v>78.74264650000001</v>
       </c>
       <c r="O36">
-        <v>14.462418058</v>
+        <v>13.386249905</v>
       </c>
       <c r="P36">
-        <v>70.61062934200001</v>
+        <v>65.35639659500001</v>
       </c>
       <c r="Q36">
-        <v>84.210629342</v>
+        <v>78.956396595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0792706481191036</v>
+        <v>0.07972426139635742</v>
       </c>
       <c r="T36">
-        <v>0.7729941828892286</v>
+        <v>0.7834702401006333</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.17</v>
       </c>
       <c r="W36">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.078655800041169</v>
+        <v>2.666251718899155</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07270771990763232</v>
+        <v>0.07280663205665627</v>
       </c>
       <c r="C37">
-        <v>1125.852661417825</v>
+        <v>1104.705432555869</v>
       </c>
       <c r="D37">
-        <v>1510.117661417825</v>
+        <v>1507.749432555869</v>
       </c>
       <c r="E37">
-        <v>586.165</v>
+        <v>604.944</v>
       </c>
       <c r="F37">
-        <v>657.265</v>
+        <v>676.044</v>
       </c>
       <c r="G37">
         <v>273</v>
@@ -4321,28 +4321,28 @@
         <v>126</v>
       </c>
       <c r="M37">
-        <v>47.2573535</v>
+        <v>48.60756360000001</v>
       </c>
       <c r="N37">
-        <v>78.74264650000001</v>
+        <v>77.39243639999999</v>
       </c>
       <c r="O37">
-        <v>13.386249905</v>
+        <v>13.156714188</v>
       </c>
       <c r="P37">
-        <v>65.35639659500001</v>
+        <v>64.235722212</v>
       </c>
       <c r="Q37">
-        <v>78.956396595</v>
+        <v>77.83572221199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07972426139635742</v>
+        <v>0.08019205008852544</v>
       </c>
       <c r="T37">
-        <v>0.7834702401006333</v>
+        <v>0.7942736740998945</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.666251718899155</v>
+        <v>2.592189171151956</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07280663205665627</v>
+        <v>0.07290554420568024</v>
       </c>
       <c r="C38">
-        <v>1104.705432555869</v>
+        <v>1083.565619971946</v>
       </c>
       <c r="D38">
-        <v>1507.749432555869</v>
+        <v>1505.388619971946</v>
       </c>
       <c r="E38">
-        <v>604.9439999999998</v>
+        <v>623.723</v>
       </c>
       <c r="F38">
-        <v>676.0439999999999</v>
+        <v>694.823</v>
       </c>
       <c r="G38">
         <v>273</v>
@@ -4403,28 +4403,28 @@
         <v>126</v>
       </c>
       <c r="M38">
-        <v>48.60756359999999</v>
+        <v>49.9577737</v>
       </c>
       <c r="N38">
-        <v>77.39243640000001</v>
+        <v>76.0422263</v>
       </c>
       <c r="O38">
-        <v>13.156714188</v>
+        <v>12.927178471</v>
       </c>
       <c r="P38">
-        <v>64.23572221200001</v>
+        <v>63.115047829</v>
       </c>
       <c r="Q38">
-        <v>77.83572221200001</v>
+        <v>76.71504782899999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08019205008852542</v>
+        <v>0.08067468921536544</v>
       </c>
       <c r="T38">
-        <v>0.7942736740998944</v>
+        <v>0.8054200742578622</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.592189171151957</v>
+        <v>2.522130004364065</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07290554420568024</v>
+        <v>0.07423451635470417</v>
       </c>
       <c r="C39">
-        <v>1083.565619971946</v>
+        <v>1033.769217614959</v>
       </c>
       <c r="D39">
-        <v>1505.388619971946</v>
+        <v>1474.371217614958</v>
       </c>
       <c r="E39">
-        <v>623.723</v>
+        <v>642.502</v>
       </c>
       <c r="F39">
-        <v>694.823</v>
+        <v>713.602</v>
       </c>
       <c r="G39">
         <v>273</v>
@@ -4485,45 +4485,45 @@
         <v>126</v>
       </c>
       <c r="M39">
-        <v>49.9577737</v>
+        <v>54.0910316</v>
       </c>
       <c r="N39">
-        <v>76.0422263</v>
+        <v>71.90896839999999</v>
       </c>
       <c r="O39">
-        <v>12.927178471</v>
+        <v>12.224524628</v>
       </c>
       <c r="P39">
-        <v>63.115047829</v>
+        <v>59.68444377199999</v>
       </c>
       <c r="Q39">
-        <v>76.71504782899999</v>
+        <v>73.28444377199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08067468921536544</v>
+        <v>0.08117289734629705</v>
       </c>
       <c r="T39">
-        <v>0.8054200742578622</v>
+        <v>0.8169260357112483</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.17</v>
       </c>
       <c r="W39">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.522130004364065</v>
+        <v>2.329406488893808</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07423451635470417</v>
+        <v>0.07436579850372813</v>
       </c>
       <c r="C40">
-        <v>1033.769217614959</v>
+        <v>1011.995400001439</v>
       </c>
       <c r="D40">
-        <v>1474.371217614958</v>
+        <v>1471.376400001439</v>
       </c>
       <c r="E40">
-        <v>642.502</v>
+        <v>661.2809999999999</v>
       </c>
       <c r="F40">
-        <v>713.602</v>
+        <v>732.381</v>
       </c>
       <c r="G40">
         <v>273</v>
@@ -4567,28 +4567,28 @@
         <v>126</v>
       </c>
       <c r="M40">
-        <v>54.0910316</v>
+        <v>55.5144798</v>
       </c>
       <c r="N40">
-        <v>71.90896839999999</v>
+        <v>70.4855202</v>
       </c>
       <c r="O40">
-        <v>12.224524628</v>
+        <v>11.982538434</v>
       </c>
       <c r="P40">
-        <v>59.68444377199999</v>
+        <v>58.502981766</v>
       </c>
       <c r="Q40">
-        <v>73.28444377199999</v>
+        <v>72.102981766</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08117289734629705</v>
+        <v>0.0816874401700461</v>
       </c>
       <c r="T40">
-        <v>0.8169260357112483</v>
+        <v>0.8288092418024503</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.329406488893808</v>
+        <v>2.26967811738371</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07436579850372813</v>
+        <v>0.07449708065275207</v>
       </c>
       <c r="C41">
-        <v>1011.995400001439</v>
+        <v>990.2337241758381</v>
       </c>
       <c r="D41">
-        <v>1471.376400001439</v>
+        <v>1468.393724175838</v>
       </c>
       <c r="E41">
-        <v>661.2809999999999</v>
+        <v>680.0599999999999</v>
       </c>
       <c r="F41">
-        <v>732.381</v>
+        <v>751.16</v>
       </c>
       <c r="G41">
         <v>273</v>
@@ -4649,28 +4649,28 @@
         <v>126</v>
       </c>
       <c r="M41">
-        <v>55.5144798</v>
+        <v>56.937928</v>
       </c>
       <c r="N41">
-        <v>70.4855202</v>
+        <v>69.062072</v>
       </c>
       <c r="O41">
-        <v>11.982538434</v>
+        <v>11.74055224</v>
       </c>
       <c r="P41">
-        <v>58.502981766</v>
+        <v>57.32151976</v>
       </c>
       <c r="Q41">
-        <v>72.102981766</v>
+        <v>70.92151976</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0816874401700461</v>
+        <v>0.08221913442125345</v>
       </c>
       <c r="T41">
-        <v>0.8288092418024503</v>
+        <v>0.8410885547633592</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.26967811738371</v>
+        <v>2.212936164449117</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07449708065275207</v>
+        <v>0.07462836280177602</v>
       </c>
       <c r="C42">
-        <v>990.2337241758381</v>
+        <v>968.4841164484718</v>
       </c>
       <c r="D42">
-        <v>1468.393724175838</v>
+        <v>1465.423116448472</v>
       </c>
       <c r="E42">
-        <v>680.0599999999999</v>
+        <v>698.8389999999999</v>
       </c>
       <c r="F42">
-        <v>751.16</v>
+        <v>769.939</v>
       </c>
       <c r="G42">
         <v>273</v>
@@ -4731,28 +4731,28 @@
         <v>126</v>
       </c>
       <c r="M42">
-        <v>56.937928</v>
+        <v>58.3613762</v>
       </c>
       <c r="N42">
-        <v>69.062072</v>
+        <v>67.6386238</v>
       </c>
       <c r="O42">
-        <v>11.74055224</v>
+        <v>11.498566046</v>
       </c>
       <c r="P42">
-        <v>57.32151976</v>
+        <v>56.140057754</v>
       </c>
       <c r="Q42">
-        <v>70.92151976</v>
+        <v>69.74005775399999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08221913442125345</v>
+        <v>0.08276885220640004</v>
       </c>
       <c r="T42">
-        <v>0.8410885547633592</v>
+        <v>0.853784115621248</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.212936164449117</v>
+        <v>2.158962111657675</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07462836280177602</v>
+        <v>0.07475964495079997</v>
       </c>
       <c r="C43">
-        <v>968.4841164484718</v>
+        <v>946.7465037247614</v>
       </c>
       <c r="D43">
-        <v>1465.423116448472</v>
+        <v>1462.464503724761</v>
       </c>
       <c r="E43">
-        <v>698.8389999999999</v>
+        <v>717.6180000000001</v>
       </c>
       <c r="F43">
-        <v>769.939</v>
+        <v>788.7180000000001</v>
       </c>
       <c r="G43">
         <v>273</v>
@@ -4813,28 +4813,28 @@
         <v>126</v>
       </c>
       <c r="M43">
-        <v>58.3613762</v>
+        <v>59.78482440000001</v>
       </c>
       <c r="N43">
-        <v>67.6386238</v>
+        <v>66.21517559999998</v>
       </c>
       <c r="O43">
-        <v>11.498566046</v>
+        <v>11.256579852</v>
       </c>
       <c r="P43">
-        <v>56.140057754</v>
+        <v>54.95859574799998</v>
       </c>
       <c r="Q43">
-        <v>69.74005775399999</v>
+        <v>68.55859574799997</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08276885220640004</v>
+        <v>0.08333752577724134</v>
       </c>
       <c r="T43">
-        <v>0.853784115621248</v>
+        <v>0.8669174544397537</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.158962111657675</v>
+        <v>2.107558251856302</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07475964495079998</v>
+        <v>0.07489092709982392</v>
       </c>
       <c r="C44">
-        <v>946.7465037247613</v>
+        <v>925.0208134992337</v>
       </c>
       <c r="D44">
-        <v>1462.464503724761</v>
+        <v>1459.517813499234</v>
       </c>
       <c r="E44">
-        <v>717.6179999999999</v>
+        <v>736.3969999999999</v>
       </c>
       <c r="F44">
-        <v>788.718</v>
+        <v>807.497</v>
       </c>
       <c r="G44">
         <v>273</v>
@@ -4895,28 +4895,28 @@
         <v>126</v>
       </c>
       <c r="M44">
-        <v>59.78482440000001</v>
+        <v>61.2082726</v>
       </c>
       <c r="N44">
-        <v>66.21517559999999</v>
+        <v>64.7917274</v>
       </c>
       <c r="O44">
-        <v>11.256579852</v>
+        <v>11.014593658</v>
       </c>
       <c r="P44">
-        <v>54.95859574799999</v>
+        <v>53.777133742</v>
       </c>
       <c r="Q44">
-        <v>68.55859574799999</v>
+        <v>67.37713374199998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08333752577724134</v>
+        <v>0.08392615280670865</v>
       </c>
       <c r="T44">
-        <v>0.8669174544397535</v>
+        <v>0.8805116121641717</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.107558251856302</v>
+        <v>2.058545269254993</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07489092709982392</v>
+        <v>0.07502220924884788</v>
       </c>
       <c r="C45">
-        <v>925.0208134992337</v>
+        <v>903.3069738496005</v>
       </c>
       <c r="D45">
-        <v>1459.517813499234</v>
+        <v>1456.5829738496</v>
       </c>
       <c r="E45">
-        <v>736.3969999999999</v>
+        <v>755.1759999999999</v>
       </c>
       <c r="F45">
-        <v>807.497</v>
+        <v>826.276</v>
       </c>
       <c r="G45">
         <v>273</v>
@@ -4977,28 +4977,28 @@
         <v>126</v>
       </c>
       <c r="M45">
-        <v>61.2082726</v>
+        <v>62.6317208</v>
       </c>
       <c r="N45">
-        <v>64.7917274</v>
+        <v>63.3682792</v>
       </c>
       <c r="O45">
-        <v>11.014593658</v>
+        <v>10.772607464</v>
       </c>
       <c r="P45">
-        <v>53.777133742</v>
+        <v>52.595671736</v>
       </c>
       <c r="Q45">
-        <v>67.37713374199998</v>
+        <v>66.19567173599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08392615280670865</v>
+        <v>0.0845358022300855</v>
       </c>
       <c r="T45">
-        <v>0.8805116121641717</v>
+        <v>0.8945912755216048</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.058545269254993</v>
+        <v>2.011760149499198</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07502220924884788</v>
+        <v>0.08045719139787183</v>
       </c>
       <c r="C46">
-        <v>903.3069738496005</v>
+        <v>772.5905657725383</v>
       </c>
       <c r="D46">
-        <v>1456.5829738496</v>
+        <v>1344.645565772538</v>
       </c>
       <c r="E46">
-        <v>755.1759999999999</v>
+        <v>773.9549999999999</v>
       </c>
       <c r="F46">
-        <v>826.276</v>
+        <v>845.0549999999999</v>
       </c>
       <c r="G46">
         <v>273</v>
@@ -5059,45 +5059,45 @@
         <v>126</v>
       </c>
       <c r="M46">
-        <v>62.6317208</v>
+        <v>76.05494999999999</v>
       </c>
       <c r="N46">
-        <v>63.3682792</v>
+        <v>49.94505000000001</v>
       </c>
       <c r="O46">
-        <v>10.772607464</v>
+        <v>8.490658500000002</v>
       </c>
       <c r="P46">
-        <v>52.595671736</v>
+        <v>41.45439150000001</v>
       </c>
       <c r="Q46">
-        <v>66.19567173599999</v>
+        <v>55.0543915</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0845358022300855</v>
+        <v>0.08516762072340331</v>
       </c>
       <c r="T46">
-        <v>0.8945912755216048</v>
+        <v>0.9091829266374899</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.17</v>
       </c>
       <c r="W46">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.011760149499198</v>
+        <v>1.656696901385117</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08045719139787183</v>
+        <v>0.08070633354689577</v>
       </c>
       <c r="C47">
-        <v>772.5905657725383</v>
+        <v>749.0912649416715</v>
       </c>
       <c r="D47">
-        <v>1344.645565772538</v>
+        <v>1339.925264941671</v>
       </c>
       <c r="E47">
-        <v>773.9549999999999</v>
+        <v>792.7339999999999</v>
       </c>
       <c r="F47">
-        <v>845.0549999999999</v>
+        <v>863.8339999999999</v>
       </c>
       <c r="G47">
         <v>273</v>
@@ -5141,28 +5141,28 @@
         <v>126</v>
       </c>
       <c r="M47">
-        <v>76.05494999999999</v>
+        <v>77.74506</v>
       </c>
       <c r="N47">
-        <v>49.94505000000001</v>
+        <v>48.25494</v>
       </c>
       <c r="O47">
-        <v>8.490658500000002</v>
+        <v>8.203339800000002</v>
       </c>
       <c r="P47">
-        <v>41.45439150000001</v>
+        <v>40.0516002</v>
       </c>
       <c r="Q47">
-        <v>55.0543915</v>
+        <v>53.6516002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08516762072340331</v>
+        <v>0.08582283990165884</v>
       </c>
       <c r="T47">
-        <v>0.9091829266374899</v>
+        <v>0.9243150092761857</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.656696901385117</v>
+        <v>1.620681751355006</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08070633354689577</v>
+        <v>0.08095547569591972</v>
       </c>
       <c r="C48">
-        <v>749.0912649416715</v>
+        <v>725.6249888678191</v>
       </c>
       <c r="D48">
-        <v>1339.925264941671</v>
+        <v>1335.237988867819</v>
       </c>
       <c r="E48">
-        <v>792.7339999999999</v>
+        <v>811.5129999999999</v>
       </c>
       <c r="F48">
-        <v>863.8339999999999</v>
+        <v>882.6129999999999</v>
       </c>
       <c r="G48">
         <v>273</v>
@@ -5223,28 +5223,28 @@
         <v>126</v>
       </c>
       <c r="M48">
-        <v>77.74506</v>
+        <v>79.43516999999999</v>
       </c>
       <c r="N48">
-        <v>48.25494</v>
+        <v>46.56483000000001</v>
       </c>
       <c r="O48">
-        <v>8.203339800000002</v>
+        <v>7.916021100000003</v>
       </c>
       <c r="P48">
-        <v>40.0516002</v>
+        <v>38.64880890000001</v>
       </c>
       <c r="Q48">
-        <v>53.6516002</v>
+        <v>52.24880890000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08582283990165884</v>
+        <v>0.08650278433192402</v>
       </c>
       <c r="T48">
-        <v>0.9243150092761857</v>
+        <v>0.9400181139012472</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.620681751355006</v>
+        <v>1.586199160900644</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08095547569591972</v>
+        <v>0.08120461784494368</v>
       </c>
       <c r="C49">
-        <v>725.6249888678191</v>
+        <v>702.1913921812577</v>
       </c>
       <c r="D49">
-        <v>1335.237988867819</v>
+        <v>1330.583392181258</v>
       </c>
       <c r="E49">
-        <v>811.5129999999999</v>
+        <v>830.292</v>
       </c>
       <c r="F49">
-        <v>882.6129999999999</v>
+        <v>901.3920000000001</v>
       </c>
       <c r="G49">
         <v>273</v>
@@ -5305,28 +5305,28 @@
         <v>126</v>
       </c>
       <c r="M49">
-        <v>79.43516999999999</v>
+        <v>81.12528</v>
       </c>
       <c r="N49">
-        <v>46.56483000000001</v>
+        <v>44.87472</v>
       </c>
       <c r="O49">
-        <v>7.916021100000003</v>
+        <v>7.6287024</v>
       </c>
       <c r="P49">
-        <v>38.64880890000001</v>
+        <v>37.24601759999999</v>
       </c>
       <c r="Q49">
-        <v>52.24880890000001</v>
+        <v>50.84601759999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08650278433192402</v>
+        <v>0.08720888047104552</v>
       </c>
       <c r="T49">
-        <v>0.9400181139012472</v>
+        <v>0.9563251840888113</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.586199160900644</v>
+        <v>1.553153345048547</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08120461784494366</v>
+        <v>0.08145375999396762</v>
       </c>
       <c r="C50">
-        <v>702.1913921812583</v>
+        <v>678.7901343113277</v>
       </c>
       <c r="D50">
-        <v>1330.583392181258</v>
+        <v>1325.961134311328</v>
       </c>
       <c r="E50">
-        <v>830.2919999999999</v>
+        <v>849.0709999999999</v>
       </c>
       <c r="F50">
-        <v>901.3919999999999</v>
+        <v>920.1709999999999</v>
       </c>
       <c r="G50">
         <v>273</v>
@@ -5387,28 +5387,28 @@
         <v>126</v>
       </c>
       <c r="M50">
-        <v>81.12527999999999</v>
+        <v>82.81538999999999</v>
       </c>
       <c r="N50">
-        <v>44.87472000000001</v>
+        <v>43.18461000000001</v>
       </c>
       <c r="O50">
-        <v>7.628702400000003</v>
+        <v>7.341383700000002</v>
       </c>
       <c r="P50">
-        <v>37.24601760000001</v>
+        <v>35.8432263</v>
       </c>
       <c r="Q50">
-        <v>50.8460176</v>
+        <v>49.4432263</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08720888047104552</v>
+        <v>0.08794266665483848</v>
       </c>
       <c r="T50">
-        <v>0.9563251840888113</v>
+        <v>0.9732717472249071</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.553153345048547</v>
+        <v>1.52145633800674</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08145375999396762</v>
+        <v>0.106517698571112</v>
       </c>
       <c r="C51">
-        <v>678.7901343113277</v>
+        <v>316.6266764015469</v>
       </c>
       <c r="D51">
-        <v>1325.961134311328</v>
+        <v>982.5766764015468</v>
       </c>
       <c r="E51">
-        <v>849.0709999999999</v>
+        <v>867.8499999999999</v>
       </c>
       <c r="F51">
-        <v>920.1709999999999</v>
+        <v>938.9499999999999</v>
       </c>
       <c r="G51">
         <v>273</v>
@@ -5469,45 +5469,45 @@
         <v>126</v>
       </c>
       <c r="M51">
-        <v>82.81538999999999</v>
+        <v>137.83786</v>
       </c>
       <c r="N51">
-        <v>43.18461000000001</v>
+        <v>-11.83786000000001</v>
       </c>
       <c r="O51">
-        <v>7.341383700000002</v>
+        <v>-2.012436200000001</v>
       </c>
       <c r="P51">
-        <v>35.8432263</v>
+        <v>-9.825423800000005</v>
       </c>
       <c r="Q51">
-        <v>49.4432263</v>
+        <v>3.77457619999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08794266665483848</v>
+        <v>0.08904811347429711</v>
       </c>
       <c r="T51">
-        <v>0.9732717472249071</v>
+        <v>0.9988016968659841</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.17</v>
+        <v>0.1553999750141217</v>
       </c>
       <c r="W51">
-        <v>0.07469999999999999</v>
+        <v>0.1239872836679269</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.52145633800674</v>
+        <v>0.9141175000830686</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.106517698571112</v>
+        <v>0.107527698571112</v>
       </c>
       <c r="C52">
-        <v>316.6266764015469</v>
+        <v>287.6996950154506</v>
       </c>
       <c r="D52">
-        <v>982.5766764015468</v>
+        <v>972.4286950154507</v>
       </c>
       <c r="E52">
-        <v>867.8499999999999</v>
+        <v>886.6289999999999</v>
       </c>
       <c r="F52">
-        <v>938.9499999999999</v>
+        <v>957.7289999999999</v>
       </c>
       <c r="G52">
         <v>273</v>
@@ -5551,37 +5551,37 @@
         <v>126</v>
       </c>
       <c r="M52">
-        <v>137.83786</v>
+        <v>140.5946172</v>
       </c>
       <c r="N52">
-        <v>-11.83786000000001</v>
+        <v>-14.59461720000002</v>
       </c>
       <c r="O52">
-        <v>-2.012436200000001</v>
+        <v>-2.481084924000003</v>
       </c>
       <c r="P52">
-        <v>-9.825423800000005</v>
+        <v>-12.11353227600001</v>
       </c>
       <c r="Q52">
-        <v>3.77457619999999</v>
+        <v>1.486467723999981</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08904811347429711</v>
+        <v>0.08993072803499706</v>
       </c>
       <c r="T52">
-        <v>0.9988016968659841</v>
+        <v>1.01918540496529</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1553999750141217</v>
+        <v>0.1523529166805114</v>
       </c>
       <c r="W52">
-        <v>0.1239872836679269</v>
+        <v>0.1244345918313009</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9141175000830686</v>
+        <v>0.89619362753242</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.107527698571112</v>
+        <v>0.108537698571112</v>
       </c>
       <c r="C53">
-        <v>287.6996950154506</v>
+        <v>258.9801861151135</v>
       </c>
       <c r="D53">
-        <v>972.4286950154507</v>
+        <v>962.4881861151135</v>
       </c>
       <c r="E53">
-        <v>886.6289999999999</v>
+        <v>905.4079999999999</v>
       </c>
       <c r="F53">
-        <v>957.7289999999999</v>
+        <v>976.5079999999999</v>
       </c>
       <c r="G53">
         <v>273</v>
@@ -5633,37 +5633,37 @@
         <v>126</v>
       </c>
       <c r="M53">
-        <v>140.5946172</v>
+        <v>143.3513744</v>
       </c>
       <c r="N53">
-        <v>-14.59461720000002</v>
+        <v>-17.3513744</v>
       </c>
       <c r="O53">
-        <v>-2.481084924000003</v>
+        <v>-2.949733648</v>
       </c>
       <c r="P53">
-        <v>-12.11353227600001</v>
+        <v>-14.401640752</v>
       </c>
       <c r="Q53">
-        <v>1.486467723999981</v>
+        <v>-0.8016407520000044</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08993072803499706</v>
+        <v>0.09085011820239283</v>
       </c>
       <c r="T53">
-        <v>1.01918540496529</v>
+        <v>1.0404184342354</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1523529166805114</v>
+        <v>0.1494230528981939</v>
       </c>
       <c r="W53">
-        <v>0.1244345918313009</v>
+        <v>0.1248646958345451</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.89619362753242</v>
+        <v>0.8789591346952583</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.108537698571112</v>
+        <v>0.109547698571112</v>
       </c>
       <c r="C54">
-        <v>258.9801861151135</v>
+        <v>230.4618515121863</v>
       </c>
       <c r="D54">
-        <v>962.4881861151135</v>
+        <v>952.7488515121864</v>
       </c>
       <c r="E54">
-        <v>905.4079999999999</v>
+        <v>924.187</v>
       </c>
       <c r="F54">
-        <v>976.5079999999999</v>
+        <v>995.287</v>
       </c>
       <c r="G54">
         <v>273</v>
@@ -5715,37 +5715,37 @@
         <v>126</v>
       </c>
       <c r="M54">
-        <v>143.3513744</v>
+        <v>146.1081316</v>
       </c>
       <c r="N54">
-        <v>-17.3513744</v>
+        <v>-20.10813160000001</v>
       </c>
       <c r="O54">
-        <v>-2.949733648</v>
+        <v>-3.418382372000001</v>
       </c>
       <c r="P54">
-        <v>-14.401640752</v>
+        <v>-16.68974922800001</v>
       </c>
       <c r="Q54">
-        <v>-0.8016407520000044</v>
+        <v>-3.089749228000013</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09085011820239283</v>
+        <v>0.09180863135563525</v>
       </c>
       <c r="T54">
-        <v>1.0404184342354</v>
+        <v>1.062554996665941</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1494230528981939</v>
+        <v>0.1466037500133223</v>
       </c>
       <c r="W54">
-        <v>0.1248646958345451</v>
+        <v>0.1252785694980443</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8789591346952583</v>
+        <v>0.8623750000783665</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.109547698571112</v>
+        <v>0.110557698571112</v>
       </c>
       <c r="C55">
-        <v>230.4618515121863</v>
+        <v>202.1386453879056</v>
       </c>
       <c r="D55">
-        <v>952.7488515121864</v>
+        <v>943.2046453879058</v>
       </c>
       <c r="E55">
-        <v>924.187</v>
+        <v>942.966</v>
       </c>
       <c r="F55">
-        <v>995.287</v>
+        <v>1014.066</v>
       </c>
       <c r="G55">
         <v>273</v>
@@ -5797,37 +5797,37 @@
         <v>126</v>
       </c>
       <c r="M55">
-        <v>146.1081316</v>
+        <v>148.8648888</v>
       </c>
       <c r="N55">
-        <v>-20.10813160000001</v>
+        <v>-22.86488880000002</v>
       </c>
       <c r="O55">
-        <v>-3.418382372000001</v>
+        <v>-3.887031096000003</v>
       </c>
       <c r="P55">
-        <v>-16.68974922800001</v>
+        <v>-18.97785770400002</v>
       </c>
       <c r="Q55">
-        <v>-3.089749228000013</v>
+        <v>-5.377857704000021</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09180863135563525</v>
+        <v>0.09280881899380121</v>
       </c>
       <c r="T55">
-        <v>1.062554996665941</v>
+        <v>1.085654018332591</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1466037500133223</v>
+        <v>0.1438888657538163</v>
       </c>
       <c r="W55">
-        <v>0.1252785694980443</v>
+        <v>0.1256771145073398</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8623750000783665</v>
+        <v>0.8464050926695079</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.110557698571112</v>
+        <v>0.111567698571112</v>
       </c>
       <c r="C56">
-        <v>202.1386453879056</v>
+        <v>174.0047617778418</v>
       </c>
       <c r="D56">
-        <v>943.2046453879058</v>
+        <v>933.8497617778419</v>
       </c>
       <c r="E56">
-        <v>942.966</v>
+        <v>961.745</v>
       </c>
       <c r="F56">
-        <v>1014.066</v>
+        <v>1032.845</v>
       </c>
       <c r="G56">
         <v>273</v>
@@ -5879,37 +5879,37 @@
         <v>126</v>
       </c>
       <c r="M56">
-        <v>148.8648888</v>
+        <v>151.621646</v>
       </c>
       <c r="N56">
-        <v>-22.86488880000002</v>
+        <v>-25.62164600000003</v>
       </c>
       <c r="O56">
-        <v>-3.887031096000003</v>
+        <v>-4.355679820000005</v>
       </c>
       <c r="P56">
-        <v>-18.97785770400002</v>
+        <v>-21.26596618000002</v>
       </c>
       <c r="Q56">
-        <v>-5.377857704000021</v>
+        <v>-7.665966180000026</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09280881899380121</v>
+        <v>0.09385345941588569</v>
       </c>
       <c r="T56">
-        <v>1.085654018332591</v>
+        <v>1.109779663184427</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1438888657538163</v>
+        <v>0.1412727045582924</v>
       </c>
       <c r="W56">
-        <v>0.1256771145073398</v>
+        <v>0.1260611669708427</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8464050926695079</v>
+        <v>0.8310159091664259</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.111567698571112</v>
+        <v>0.1125776985711121</v>
       </c>
       <c r="C57">
-        <v>174.0047617778418</v>
+        <v>146.0546227941111</v>
       </c>
       <c r="D57">
-        <v>933.8497617778419</v>
+        <v>924.6786227941112</v>
       </c>
       <c r="E57">
-        <v>961.745</v>
+        <v>980.524</v>
       </c>
       <c r="F57">
-        <v>1032.845</v>
+        <v>1051.624</v>
       </c>
       <c r="G57">
         <v>273</v>
@@ -5961,37 +5961,37 @@
         <v>126</v>
       </c>
       <c r="M57">
-        <v>151.621646</v>
+        <v>154.3784032</v>
       </c>
       <c r="N57">
-        <v>-25.62164600000003</v>
+        <v>-28.37840320000001</v>
       </c>
       <c r="O57">
-        <v>-4.355679820000005</v>
+        <v>-4.824328544000002</v>
       </c>
       <c r="P57">
-        <v>-21.26596618000002</v>
+        <v>-23.554074656</v>
       </c>
       <c r="Q57">
-        <v>-7.665966180000026</v>
+        <v>-9.95407465600001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09385345941588569</v>
+        <v>0.09494558349351948</v>
       </c>
       <c r="T57">
-        <v>1.109779663184427</v>
+        <v>1.1350019282568</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1412727045582924</v>
+        <v>0.1387499776911801</v>
       </c>
       <c r="W57">
-        <v>0.1260611669708427</v>
+        <v>0.1264315032749348</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8310159091664259</v>
+        <v>0.8161763393598827</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1125776985711121</v>
+        <v>0.113587698571112</v>
       </c>
       <c r="C58">
-        <v>146.0546227941111</v>
+        <v>118.2828675348369</v>
       </c>
       <c r="D58">
-        <v>924.6786227941112</v>
+        <v>915.6858675348369</v>
       </c>
       <c r="E58">
-        <v>980.524</v>
+        <v>999.303</v>
       </c>
       <c r="F58">
-        <v>1051.624</v>
+        <v>1070.403</v>
       </c>
       <c r="G58">
         <v>273</v>
@@ -6043,37 +6043,37 @@
         <v>126</v>
       </c>
       <c r="M58">
-        <v>154.3784032</v>
+        <v>157.1351604</v>
       </c>
       <c r="N58">
-        <v>-28.37840320000001</v>
+        <v>-31.13516040000002</v>
       </c>
       <c r="O58">
-        <v>-4.824328544000002</v>
+        <v>-5.292977268000003</v>
       </c>
       <c r="P58">
-        <v>-23.554074656</v>
+        <v>-25.84218313200002</v>
       </c>
       <c r="Q58">
-        <v>-9.95407465600001</v>
+        <v>-12.24218313200002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09494558349351948</v>
+        <v>0.09608850403988038</v>
       </c>
       <c r="T58">
-        <v>1.1350019282568</v>
+        <v>1.161397321937191</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1387499776911801</v>
+        <v>0.1363157675562471</v>
       </c>
       <c r="W58">
-        <v>0.1264315032749348</v>
+        <v>0.1267888453227429</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8161763393598827</v>
+        <v>0.801857456213218</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.113587698571112</v>
+        <v>0.1464076081804291</v>
       </c>
       <c r="C59">
-        <v>118.2828675348369</v>
+        <v>-120.3839507532383</v>
       </c>
       <c r="D59">
-        <v>915.6858675348369</v>
+        <v>695.7980492467617</v>
       </c>
       <c r="E59">
-        <v>999.303</v>
+        <v>1018.082</v>
       </c>
       <c r="F59">
-        <v>1070.403</v>
+        <v>1089.182</v>
       </c>
       <c r="G59">
         <v>273</v>
@@ -6125,45 +6125,45 @@
         <v>126</v>
       </c>
       <c r="M59">
-        <v>157.1351604</v>
+        <v>218.7077456</v>
       </c>
       <c r="N59">
-        <v>-31.13516040000002</v>
+        <v>-92.70774560000001</v>
       </c>
       <c r="O59">
-        <v>-5.292977268000003</v>
+        <v>-15.760316752</v>
       </c>
       <c r="P59">
-        <v>-25.84218313200002</v>
+        <v>-76.947428848</v>
       </c>
       <c r="Q59">
-        <v>-12.24218313200002</v>
+        <v>-63.34742884800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09608850403988038</v>
+        <v>0.09845230082491804</v>
       </c>
       <c r="T59">
-        <v>1.161397321937191</v>
+        <v>1.215988471707114</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1363157675562471</v>
+        <v>0.09793891817245269</v>
       </c>
       <c r="W59">
-        <v>0.1267888453227429</v>
+        <v>0.1811338652309715</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.801857456213218</v>
+        <v>0.5761112833673687</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.146407608180429</v>
+        <v>0.1479576081804291</v>
       </c>
       <c r="C60">
-        <v>-120.3839507532379</v>
+        <v>-146.9654654579144</v>
       </c>
       <c r="D60">
-        <v>695.7980492467619</v>
+        <v>687.9955345420854</v>
       </c>
       <c r="E60">
-        <v>1018.082</v>
+        <v>1036.861</v>
       </c>
       <c r="F60">
-        <v>1089.182</v>
+        <v>1107.961</v>
       </c>
       <c r="G60">
         <v>273</v>
@@ -6207,37 +6207,37 @@
         <v>126</v>
       </c>
       <c r="M60">
-        <v>218.7077456</v>
+        <v>222.4785688</v>
       </c>
       <c r="N60">
-        <v>-92.70774559999995</v>
+        <v>-96.47856879999998</v>
       </c>
       <c r="O60">
-        <v>-15.76031675199999</v>
+        <v>-16.401356696</v>
       </c>
       <c r="P60">
-        <v>-76.94742884799996</v>
+        <v>-80.07721210399998</v>
       </c>
       <c r="Q60">
-        <v>-63.34742884799996</v>
+        <v>-66.47721210399999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09845230082491804</v>
+        <v>0.09973650328406239</v>
       </c>
       <c r="T60">
-        <v>1.215988471707114</v>
+        <v>1.245646727114605</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.09793891817245273</v>
+        <v>0.09627893650851282</v>
       </c>
       <c r="W60">
-        <v>0.1811338652309715</v>
+        <v>0.1814671895490906</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5761112833673689</v>
+        <v>0.5663466853441931</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1479576081804291</v>
+        <v>0.149507608180429</v>
       </c>
       <c r="C61">
-        <v>-146.9654654579144</v>
+        <v>-173.3739296028392</v>
       </c>
       <c r="D61">
-        <v>687.9955345420854</v>
+        <v>680.3660703971606</v>
       </c>
       <c r="E61">
-        <v>1036.861</v>
+        <v>1055.64</v>
       </c>
       <c r="F61">
-        <v>1107.961</v>
+        <v>1126.74</v>
       </c>
       <c r="G61">
         <v>273</v>
@@ -6289,37 +6289,37 @@
         <v>126</v>
       </c>
       <c r="M61">
-        <v>222.4785688</v>
+        <v>226.249392</v>
       </c>
       <c r="N61">
-        <v>-96.47856879999998</v>
+        <v>-100.249392</v>
       </c>
       <c r="O61">
-        <v>-16.401356696</v>
+        <v>-17.04239664</v>
       </c>
       <c r="P61">
-        <v>-80.07721210399998</v>
+        <v>-83.20699535999998</v>
       </c>
       <c r="Q61">
-        <v>-66.47721210399999</v>
+        <v>-69.60699535999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09973650328406239</v>
+        <v>0.1010849158661639</v>
       </c>
       <c r="T61">
-        <v>1.245646727114605</v>
+        <v>1.27678789529247</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.09627893650851282</v>
+        <v>0.09467428756670429</v>
       </c>
       <c r="W61">
-        <v>0.1814671895490906</v>
+        <v>0.1817894030566058</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5663466853441931</v>
+        <v>0.5569075739217899</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.149507608180429</v>
+        <v>0.151057608180429</v>
       </c>
       <c r="C62">
-        <v>-173.3739296028392</v>
+        <v>-199.6150371310566</v>
       </c>
       <c r="D62">
-        <v>680.3660703971606</v>
+        <v>672.9039628689432</v>
       </c>
       <c r="E62">
-        <v>1055.64</v>
+        <v>1074.419</v>
       </c>
       <c r="F62">
-        <v>1126.74</v>
+        <v>1145.519</v>
       </c>
       <c r="G62">
         <v>273</v>
@@ -6371,37 +6371,37 @@
         <v>126</v>
       </c>
       <c r="M62">
-        <v>226.249392</v>
+        <v>230.0202152</v>
       </c>
       <c r="N62">
-        <v>-100.249392</v>
+        <v>-104.0202152</v>
       </c>
       <c r="O62">
-        <v>-17.04239664</v>
+        <v>-17.683436584</v>
       </c>
       <c r="P62">
-        <v>-83.20699535999998</v>
+        <v>-86.33677861599998</v>
       </c>
       <c r="Q62">
-        <v>-69.60699535999998</v>
+        <v>-72.73677861599998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1010849158661639</v>
+        <v>0.1025024778114502</v>
       </c>
       <c r="T62">
-        <v>1.27678789529247</v>
+        <v>1.309526046453815</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.09467428756670429</v>
+        <v>0.09312225006561078</v>
       </c>
       <c r="W62">
-        <v>0.1817894030566058</v>
+        <v>0.1821010521868253</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5569075739217899</v>
+        <v>0.5477779415624162</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.151057608180429</v>
+        <v>0.152607608180429</v>
       </c>
       <c r="C63">
-        <v>-199.6150371310566</v>
+        <v>-225.6942348959068</v>
       </c>
       <c r="D63">
-        <v>672.9039628689432</v>
+        <v>665.6037651040932</v>
       </c>
       <c r="E63">
-        <v>1074.419</v>
+        <v>1093.198</v>
       </c>
       <c r="F63">
-        <v>1145.519</v>
+        <v>1164.298</v>
       </c>
       <c r="G63">
         <v>273</v>
@@ -6453,37 +6453,37 @@
         <v>126</v>
       </c>
       <c r="M63">
-        <v>230.0202152</v>
+        <v>233.7910384</v>
       </c>
       <c r="N63">
-        <v>-104.0202152</v>
+        <v>-107.7910384</v>
       </c>
       <c r="O63">
-        <v>-17.683436584</v>
+        <v>-18.32447652800001</v>
       </c>
       <c r="P63">
-        <v>-86.33677861599998</v>
+        <v>-89.46656187200001</v>
       </c>
       <c r="Q63">
-        <v>-72.73677861599998</v>
+        <v>-75.86656187200002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1025024778114502</v>
+        <v>0.1039946482801726</v>
       </c>
       <c r="T63">
-        <v>1.309526046453815</v>
+        <v>1.3439872582026</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.09312225006561078</v>
+        <v>0.09162027829035897</v>
       </c>
       <c r="W63">
-        <v>0.1821010521868253</v>
+        <v>0.1824026481192959</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5477779415624162</v>
+        <v>0.5389428134726998</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.152607608180429</v>
+        <v>0.1541576081804291</v>
       </c>
       <c r="C64">
-        <v>-225.6942348959068</v>
+        <v>-251.6167359203067</v>
       </c>
       <c r="D64">
-        <v>665.6037651040932</v>
+        <v>658.4602640796933</v>
       </c>
       <c r="E64">
-        <v>1093.198</v>
+        <v>1111.977</v>
       </c>
       <c r="F64">
-        <v>1164.298</v>
+        <v>1183.077</v>
       </c>
       <c r="G64">
         <v>273</v>
@@ -6535,37 +6535,37 @@
         <v>126</v>
       </c>
       <c r="M64">
-        <v>233.7910384</v>
+        <v>237.5618616</v>
       </c>
       <c r="N64">
-        <v>-107.7910384</v>
+        <v>-111.5618616</v>
       </c>
       <c r="O64">
-        <v>-18.32447652800001</v>
+        <v>-18.965516472</v>
       </c>
       <c r="P64">
-        <v>-89.46656187200001</v>
+        <v>-92.59634512800001</v>
       </c>
       <c r="Q64">
-        <v>-75.86656187200002</v>
+        <v>-78.99634512800002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1039946482801726</v>
+        <v>0.1055674766120691</v>
       </c>
       <c r="T64">
-        <v>1.3439872582026</v>
+        <v>1.380311238154021</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09162027829035897</v>
+        <v>0.09016598815876596</v>
       </c>
       <c r="W64">
-        <v>0.1824026481192959</v>
+        <v>0.1826946695777198</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5389428134726998</v>
+        <v>0.5303881656397997</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1541576081804291</v>
+        <v>0.1557076081804291</v>
       </c>
       <c r="C65">
-        <v>-251.6167359203067</v>
+        <v>-277.3875318112788</v>
       </c>
       <c r="D65">
-        <v>658.4602640796933</v>
+        <v>651.4684681887212</v>
       </c>
       <c r="E65">
-        <v>1111.977</v>
+        <v>1130.756</v>
       </c>
       <c r="F65">
-        <v>1183.077</v>
+        <v>1201.856</v>
       </c>
       <c r="G65">
         <v>273</v>
@@ -6617,37 +6617,37 @@
         <v>126</v>
       </c>
       <c r="M65">
-        <v>237.5618616</v>
+        <v>241.3326848</v>
       </c>
       <c r="N65">
-        <v>-111.5618616</v>
+        <v>-115.3326848</v>
       </c>
       <c r="O65">
-        <v>-18.965516472</v>
+        <v>-19.606556416</v>
       </c>
       <c r="P65">
-        <v>-92.59634512800001</v>
+        <v>-95.72612838400001</v>
       </c>
       <c r="Q65">
-        <v>-78.99634512800002</v>
+        <v>-82.12612838400001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1055674766120691</v>
+        <v>0.1072276842957377</v>
       </c>
       <c r="T65">
-        <v>1.380311238154021</v>
+        <v>1.418653216991633</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09016598815876596</v>
+        <v>0.08875714459378524</v>
       </c>
       <c r="W65">
-        <v>0.1826946695777198</v>
+        <v>0.1829775653655679</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5303881656397997</v>
+        <v>0.522100850551678</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1557076081804291</v>
+        <v>0.1572576081804291</v>
       </c>
       <c r="C66">
-        <v>-277.3875318112788</v>
+        <v>-303.0114043918529</v>
       </c>
       <c r="D66">
-        <v>651.4684681887212</v>
+        <v>644.6235956081471</v>
       </c>
       <c r="E66">
-        <v>1130.756</v>
+        <v>1149.535</v>
       </c>
       <c r="F66">
-        <v>1201.856</v>
+        <v>1220.635</v>
       </c>
       <c r="G66">
         <v>273</v>
@@ -6699,37 +6699,37 @@
         <v>126</v>
       </c>
       <c r="M66">
-        <v>241.3326848</v>
+        <v>245.103508</v>
       </c>
       <c r="N66">
-        <v>-115.3326848</v>
+        <v>-119.103508</v>
       </c>
       <c r="O66">
-        <v>-19.606556416</v>
+        <v>-20.24759636</v>
       </c>
       <c r="P66">
-        <v>-95.72612838400001</v>
+        <v>-98.85591164</v>
       </c>
       <c r="Q66">
-        <v>-82.12612838400001</v>
+        <v>-85.25591164000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1072276842957377</v>
+        <v>0.1089827609899017</v>
       </c>
       <c r="T66">
-        <v>1.418653216991633</v>
+        <v>1.459186166048537</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08875714459378524</v>
+        <v>0.08739165006157316</v>
       </c>
       <c r="W66">
-        <v>0.1829775653655679</v>
+        <v>0.1832517566676361</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.522100850551678</v>
+        <v>0.5140685297739598</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1572576081804291</v>
+        <v>0.158807608180429</v>
       </c>
       <c r="C67">
-        <v>-303.0114043918529</v>
+        <v>-328.4929366073069</v>
       </c>
       <c r="D67">
-        <v>644.6235956081471</v>
+        <v>637.9210633926931</v>
       </c>
       <c r="E67">
-        <v>1149.535</v>
+        <v>1168.314</v>
       </c>
       <c r="F67">
-        <v>1220.635</v>
+        <v>1239.414</v>
       </c>
       <c r="G67">
         <v>273</v>
@@ -6781,37 +6781,37 @@
         <v>126</v>
       </c>
       <c r="M67">
-        <v>245.103508</v>
+        <v>248.8743312</v>
       </c>
       <c r="N67">
-        <v>-119.103508</v>
+        <v>-122.8743312</v>
       </c>
       <c r="O67">
-        <v>-20.24759636</v>
+        <v>-20.888636304</v>
       </c>
       <c r="P67">
-        <v>-98.85591164</v>
+        <v>-101.985694896</v>
       </c>
       <c r="Q67">
-        <v>-85.25591164000001</v>
+        <v>-88.385694896</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1089827609899017</v>
+        <v>0.1108410774896046</v>
       </c>
       <c r="T67">
-        <v>1.459186166048537</v>
+        <v>1.502103406226435</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08739165006157316</v>
+        <v>0.08606753415154934</v>
       </c>
       <c r="W67">
-        <v>0.1832517566676361</v>
+        <v>0.1835176391423689</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5140685297739598</v>
+        <v>0.5062796126561726</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.158807608180429</v>
+        <v>0.1840052926252403</v>
       </c>
       <c r="C68">
-        <v>-328.4929366073069</v>
+        <v>-439.5085274552451</v>
       </c>
       <c r="D68">
-        <v>637.9210633926931</v>
+        <v>545.6844725447548</v>
       </c>
       <c r="E68">
-        <v>1168.314</v>
+        <v>1187.093</v>
       </c>
       <c r="F68">
-        <v>1239.414</v>
+        <v>1258.193</v>
       </c>
       <c r="G68">
         <v>273</v>
@@ -6863,45 +6863,45 @@
         <v>126</v>
       </c>
       <c r="M68">
-        <v>248.8743312</v>
+        <v>296.6819094</v>
       </c>
       <c r="N68">
-        <v>-122.8743312</v>
+        <v>-170.6819094</v>
       </c>
       <c r="O68">
-        <v>-20.888636304</v>
+        <v>-29.015924598</v>
       </c>
       <c r="P68">
-        <v>-101.985694896</v>
+        <v>-141.665984802</v>
       </c>
       <c r="Q68">
-        <v>-88.385694896</v>
+        <v>-128.065984802</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1108410774896046</v>
+        <v>0.1134110630038692</v>
       </c>
       <c r="T68">
-        <v>1.502103406226435</v>
+        <v>1.561456420412685</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08606753415154934</v>
+        <v>0.0721985376301478</v>
       </c>
       <c r="W68">
-        <v>0.1835176391423689</v>
+        <v>0.2187755848268111</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5062796126561726</v>
+        <v>0.42469728017734</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1840052926252403</v>
+        <v>0.1859052926252403</v>
       </c>
       <c r="C69">
-        <v>-439.5085274552451</v>
+        <v>-464.1727319739761</v>
       </c>
       <c r="D69">
-        <v>545.6844725447548</v>
+        <v>539.7992680260239</v>
       </c>
       <c r="E69">
-        <v>1187.093</v>
+        <v>1205.872</v>
       </c>
       <c r="F69">
-        <v>1258.193</v>
+        <v>1276.972</v>
       </c>
       <c r="G69">
         <v>273</v>
@@ -6945,37 +6945,37 @@
         <v>126</v>
       </c>
       <c r="M69">
-        <v>296.6819094</v>
+        <v>301.1099976</v>
       </c>
       <c r="N69">
-        <v>-170.6819094</v>
+        <v>-175.1099976</v>
       </c>
       <c r="O69">
-        <v>-29.015924598</v>
+        <v>-29.768699592</v>
       </c>
       <c r="P69">
-        <v>-141.665984802</v>
+        <v>-145.341298008</v>
       </c>
       <c r="Q69">
-        <v>-128.065984802</v>
+        <v>-131.741298008</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1134110630038692</v>
+        <v>0.1155239087227402</v>
       </c>
       <c r="T69">
-        <v>1.561456420412685</v>
+        <v>1.610251933550581</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0721985376301478</v>
+        <v>0.07113679442970446</v>
       </c>
       <c r="W69">
-        <v>0.2187755848268111</v>
+        <v>0.2190259438734757</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.42469728017734</v>
+        <v>0.418451731939438</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1859052926252403</v>
+        <v>0.1878052926252403</v>
       </c>
       <c r="C70">
-        <v>-464.1727319739761</v>
+        <v>-488.7113471658546</v>
       </c>
       <c r="D70">
-        <v>539.7992680260239</v>
+        <v>534.0396528341454</v>
       </c>
       <c r="E70">
-        <v>1205.872</v>
+        <v>1224.651</v>
       </c>
       <c r="F70">
-        <v>1276.972</v>
+        <v>1295.751</v>
       </c>
       <c r="G70">
         <v>273</v>
@@ -7027,37 +7027,37 @@
         <v>126</v>
       </c>
       <c r="M70">
-        <v>301.1099976</v>
+        <v>305.5380858</v>
       </c>
       <c r="N70">
-        <v>-175.1099976</v>
+        <v>-179.5380858</v>
       </c>
       <c r="O70">
-        <v>-29.768699592</v>
+        <v>-30.52147458600001</v>
       </c>
       <c r="P70">
-        <v>-145.341298008</v>
+        <v>-149.016611214</v>
       </c>
       <c r="Q70">
-        <v>-131.741298008</v>
+        <v>-135.416611214</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1155239087227402</v>
+        <v>0.117773067068635</v>
       </c>
       <c r="T70">
-        <v>1.610251933550581</v>
+        <v>1.662195544310277</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07113679442970446</v>
+        <v>0.07010582639449134</v>
       </c>
       <c r="W70">
-        <v>0.2190259438734757</v>
+        <v>0.219269046136179</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.418451731939438</v>
+        <v>0.4123872140852431</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1878052926252403</v>
+        <v>0.1897052926252403</v>
       </c>
       <c r="C71">
-        <v>-488.7113471658546</v>
+        <v>-513.1283506740854</v>
       </c>
       <c r="D71">
-        <v>534.0396528341454</v>
+        <v>528.4016493259146</v>
       </c>
       <c r="E71">
-        <v>1224.651</v>
+        <v>1243.43</v>
       </c>
       <c r="F71">
-        <v>1295.751</v>
+        <v>1314.53</v>
       </c>
       <c r="G71">
         <v>273</v>
@@ -7109,37 +7109,37 @@
         <v>126</v>
       </c>
       <c r="M71">
-        <v>305.5380858</v>
+        <v>309.966174</v>
       </c>
       <c r="N71">
-        <v>-179.5380858</v>
+        <v>-183.966174</v>
       </c>
       <c r="O71">
-        <v>-30.52147458600001</v>
+        <v>-31.27424958000001</v>
       </c>
       <c r="P71">
-        <v>-149.016611214</v>
+        <v>-152.69192442</v>
       </c>
       <c r="Q71">
-        <v>-135.416611214</v>
+        <v>-139.09192442</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.117773067068635</v>
+        <v>0.1201721693042562</v>
       </c>
       <c r="T71">
-        <v>1.662195544310277</v>
+        <v>1.717602062453953</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07010582639449134</v>
+        <v>0.06910431458885574</v>
       </c>
       <c r="W71">
-        <v>0.219269046136179</v>
+        <v>0.2195052026199478</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4123872140852431</v>
+        <v>0.4064959681697397</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1897052926252403</v>
+        <v>0.1916052926252403</v>
       </c>
       <c r="C72">
-        <v>-513.1283506740854</v>
+        <v>-537.4275539243838</v>
       </c>
       <c r="D72">
-        <v>528.4016493259146</v>
+        <v>522.8814460756162</v>
       </c>
       <c r="E72">
-        <v>1243.43</v>
+        <v>1262.209</v>
       </c>
       <c r="F72">
-        <v>1314.53</v>
+        <v>1333.309</v>
       </c>
       <c r="G72">
         <v>273</v>
@@ -7191,37 +7191,37 @@
         <v>126</v>
       </c>
       <c r="M72">
-        <v>309.966174</v>
+        <v>314.3942622</v>
       </c>
       <c r="N72">
-        <v>-183.966174</v>
+        <v>-188.3942622</v>
       </c>
       <c r="O72">
-        <v>-31.27424958000001</v>
+        <v>-32.027024574</v>
       </c>
       <c r="P72">
-        <v>-152.69192442</v>
+        <v>-156.367237626</v>
       </c>
       <c r="Q72">
-        <v>-139.09192442</v>
+        <v>-142.767237626</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1201721693042562</v>
+        <v>0.1227367268664719</v>
       </c>
       <c r="T72">
-        <v>1.717602062453953</v>
+        <v>1.776829719779952</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06910431458885574</v>
+        <v>0.06813101438337892</v>
       </c>
       <c r="W72">
-        <v>0.2195052026199478</v>
+        <v>0.2197347068083993</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4064959681697397</v>
+        <v>0.4007706728434053</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1916052926252403</v>
+        <v>0.1935052926252403</v>
       </c>
       <c r="C73">
-        <v>-537.4275539243833</v>
+        <v>-561.6126107175641</v>
       </c>
       <c r="D73">
-        <v>522.8814460756164</v>
+        <v>517.4753892824357</v>
       </c>
       <c r="E73">
-        <v>1262.209</v>
+        <v>1280.988</v>
       </c>
       <c r="F73">
-        <v>1333.309</v>
+        <v>1352.088</v>
       </c>
       <c r="G73">
         <v>273</v>
@@ -7273,37 +7273,37 @@
         <v>126</v>
       </c>
       <c r="M73">
-        <v>314.3942622</v>
+        <v>318.8223503999999</v>
       </c>
       <c r="N73">
-        <v>-188.3942622</v>
+        <v>-192.8223503999999</v>
       </c>
       <c r="O73">
-        <v>-32.027024574</v>
+        <v>-32.77979956799999</v>
       </c>
       <c r="P73">
-        <v>-156.367237626</v>
+        <v>-160.042550832</v>
       </c>
       <c r="Q73">
-        <v>-142.767237626</v>
+        <v>-146.442550832</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1227367268664719</v>
+        <v>0.125484467111703</v>
       </c>
       <c r="T73">
-        <v>1.776829719779951</v>
+        <v>1.840287924057806</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06813101438337892</v>
+        <v>0.06718475029472089</v>
       </c>
       <c r="W73">
-        <v>0.2197347068083993</v>
+        <v>0.2199578358805048</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4007706728434054</v>
+        <v>0.3952044134983581</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1935052926252403</v>
+        <v>0.1954052926252403</v>
       </c>
       <c r="C74">
-        <v>-561.6126107175641</v>
+        <v>-585.6870252945562</v>
       </c>
       <c r="D74">
-        <v>517.4753892824357</v>
+        <v>512.1799747054438</v>
       </c>
       <c r="E74">
-        <v>1280.988</v>
+        <v>1299.767</v>
       </c>
       <c r="F74">
-        <v>1352.088</v>
+        <v>1370.867</v>
       </c>
       <c r="G74">
         <v>273</v>
@@ -7355,37 +7355,37 @@
         <v>126</v>
       </c>
       <c r="M74">
-        <v>318.8223503999999</v>
+        <v>323.2504386</v>
       </c>
       <c r="N74">
-        <v>-192.8223503999999</v>
+        <v>-197.2504386</v>
       </c>
       <c r="O74">
-        <v>-32.77979956799999</v>
+        <v>-33.532574562</v>
       </c>
       <c r="P74">
-        <v>-160.042550832</v>
+        <v>-163.717864038</v>
       </c>
       <c r="Q74">
-        <v>-146.442550832</v>
+        <v>-150.117864038</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.125484467111703</v>
+        <v>0.1284357436713957</v>
       </c>
       <c r="T74">
-        <v>1.840287924057806</v>
+        <v>1.908446736059947</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06718475029472089</v>
+        <v>0.06626441124958772</v>
       </c>
       <c r="W74">
-        <v>0.2199578358805048</v>
+        <v>0.2201748518273472</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3952044134983581</v>
+        <v>0.3897906544093395</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1954052926252403</v>
+        <v>0.1973052926252403</v>
       </c>
       <c r="C75">
-        <v>-585.6870252945562</v>
+        <v>-609.6541599112472</v>
       </c>
       <c r="D75">
-        <v>512.1799747054438</v>
+        <v>506.9918400887527</v>
       </c>
       <c r="E75">
-        <v>1299.767</v>
+        <v>1318.546</v>
       </c>
       <c r="F75">
-        <v>1370.867</v>
+        <v>1389.646</v>
       </c>
       <c r="G75">
         <v>273</v>
@@ -7437,37 +7437,37 @@
         <v>126</v>
       </c>
       <c r="M75">
-        <v>323.2504386</v>
+        <v>327.6785268</v>
       </c>
       <c r="N75">
-        <v>-197.2504386</v>
+        <v>-201.6785268</v>
       </c>
       <c r="O75">
-        <v>-33.532574562</v>
+        <v>-34.285349556</v>
       </c>
       <c r="P75">
-        <v>-163.717864038</v>
+        <v>-167.393177244</v>
       </c>
       <c r="Q75">
-        <v>-150.117864038</v>
+        <v>-153.793177244</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1284357436713957</v>
+        <v>0.131614041504911</v>
       </c>
       <c r="T75">
-        <v>1.908446736059947</v>
+        <v>1.981848533600715</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06626441124958772</v>
+        <v>0.0653689462327014</v>
       </c>
       <c r="W75">
-        <v>0.2201748518273472</v>
+        <v>0.220386002478329</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3897906544093395</v>
+        <v>0.3845232131335375</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1973052926252403</v>
+        <v>0.1992052926252403</v>
       </c>
       <c r="C76">
-        <v>-609.6541599112472</v>
+        <v>-633.5172419575697</v>
       </c>
       <c r="D76">
-        <v>506.9918400887527</v>
+        <v>501.9077580424303</v>
       </c>
       <c r="E76">
-        <v>1318.546</v>
+        <v>1337.325</v>
       </c>
       <c r="F76">
-        <v>1389.646</v>
+        <v>1408.425</v>
       </c>
       <c r="G76">
         <v>273</v>
@@ -7519,37 +7519,37 @@
         <v>126</v>
       </c>
       <c r="M76">
-        <v>327.6785268</v>
+        <v>332.106615</v>
       </c>
       <c r="N76">
-        <v>-201.6785268</v>
+        <v>-206.106615</v>
       </c>
       <c r="O76">
-        <v>-34.285349556</v>
+        <v>-35.03812455</v>
       </c>
       <c r="P76">
-        <v>-167.393177244</v>
+        <v>-171.06849045</v>
       </c>
       <c r="Q76">
-        <v>-153.793177244</v>
+        <v>-157.46849045</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.131614041504911</v>
+        <v>0.1350466031651074</v>
       </c>
       <c r="T76">
-        <v>1.981848533600715</v>
+        <v>2.061122474944743</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0653689462327014</v>
+        <v>0.06449736028293204</v>
       </c>
       <c r="W76">
-        <v>0.220386002478329</v>
+        <v>0.2205915224452846</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3845232131335375</v>
+        <v>0.3793962369584237</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1992052926252403</v>
+        <v>0.2011052926252403</v>
       </c>
       <c r="C77">
-        <v>-633.5172419575697</v>
+        <v>-657.2793706524988</v>
       </c>
       <c r="D77">
-        <v>501.9077580424303</v>
+        <v>496.9246293475012</v>
       </c>
       <c r="E77">
-        <v>1337.325</v>
+        <v>1356.104</v>
       </c>
       <c r="F77">
-        <v>1408.425</v>
+        <v>1427.204</v>
       </c>
       <c r="G77">
         <v>273</v>
@@ -7601,37 +7601,37 @@
         <v>126</v>
       </c>
       <c r="M77">
-        <v>332.106615</v>
+        <v>336.5347032</v>
       </c>
       <c r="N77">
-        <v>-206.106615</v>
+        <v>-210.5347032</v>
       </c>
       <c r="O77">
-        <v>-35.03812455</v>
+        <v>-35.79089954400001</v>
       </c>
       <c r="P77">
-        <v>-171.06849045</v>
+        <v>-174.743803656</v>
       </c>
       <c r="Q77">
-        <v>-157.46849045</v>
+        <v>-161.143803656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1350466031651074</v>
+        <v>0.1387652116303202</v>
       </c>
       <c r="T77">
-        <v>2.061122474944743</v>
+        <v>2.147002578067441</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06449736028293204</v>
+        <v>0.06364871080552503</v>
       </c>
       <c r="W77">
-        <v>0.2205915224452846</v>
+        <v>0.2207916339920572</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3793962369584237</v>
+        <v>0.3744041812089708</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2011052926252403</v>
+        <v>0.2030052926252403</v>
       </c>
       <c r="C78">
-        <v>-657.2793706524988</v>
+        <v>-680.94352334415</v>
       </c>
       <c r="D78">
-        <v>496.9246293475012</v>
+        <v>492.0394766558499</v>
       </c>
       <c r="E78">
-        <v>1356.104</v>
+        <v>1374.883</v>
       </c>
       <c r="F78">
-        <v>1427.204</v>
+        <v>1445.983</v>
       </c>
       <c r="G78">
         <v>273</v>
@@ -7683,37 +7683,37 @@
         <v>126</v>
       </c>
       <c r="M78">
-        <v>336.5347032</v>
+        <v>340.9627914</v>
       </c>
       <c r="N78">
-        <v>-210.5347032</v>
+        <v>-214.9627914</v>
       </c>
       <c r="O78">
-        <v>-35.79089954400001</v>
+        <v>-36.543674538</v>
       </c>
       <c r="P78">
-        <v>-174.743803656</v>
+        <v>-178.419116862</v>
       </c>
       <c r="Q78">
-        <v>-161.143803656</v>
+        <v>-164.819116862</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1387652116303202</v>
+        <v>0.1428071773533776</v>
       </c>
       <c r="T78">
-        <v>2.147002578067441</v>
+        <v>2.240350516244287</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06364871080552503</v>
+        <v>0.06282210417168704</v>
       </c>
       <c r="W78">
-        <v>0.2207916339920572</v>
+        <v>0.2209865478363162</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3744041812089708</v>
+        <v>0.3695417892452179</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2030052926252403</v>
+        <v>0.2049052926252403</v>
       </c>
       <c r="C79">
-        <v>-680.94352334415</v>
+        <v>-704.5125614418853</v>
       </c>
       <c r="D79">
-        <v>492.0394766558499</v>
+        <v>487.2494385581147</v>
       </c>
       <c r="E79">
-        <v>1374.883</v>
+        <v>1393.662</v>
       </c>
       <c r="F79">
-        <v>1445.983</v>
+        <v>1464.762</v>
       </c>
       <c r="G79">
         <v>273</v>
@@ -7765,37 +7765,37 @@
         <v>126</v>
       </c>
       <c r="M79">
-        <v>340.9627914</v>
+        <v>345.3908796</v>
       </c>
       <c r="N79">
-        <v>-214.9627914</v>
+        <v>-219.3908796</v>
       </c>
       <c r="O79">
-        <v>-36.543674538</v>
+        <v>-37.296449532</v>
       </c>
       <c r="P79">
-        <v>-178.419116862</v>
+        <v>-182.094430068</v>
       </c>
       <c r="Q79">
-        <v>-164.819116862</v>
+        <v>-168.494430068</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1428071773533776</v>
+        <v>0.1472165945058039</v>
       </c>
       <c r="T79">
-        <v>2.240350516244287</v>
+        <v>2.342184630619027</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06282210417168704</v>
+        <v>0.06201669257974234</v>
       </c>
       <c r="W79">
-        <v>0.2209865478363162</v>
+        <v>0.2211764638896968</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3695417892452179</v>
+        <v>0.3648040739984844</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2049052926252403</v>
+        <v>0.2068052926252403</v>
       </c>
       <c r="C80">
-        <v>-704.5125614418853</v>
+        <v>-727.9892360052638</v>
       </c>
       <c r="D80">
-        <v>487.2494385581147</v>
+        <v>482.5517639947361</v>
       </c>
       <c r="E80">
-        <v>1393.662</v>
+        <v>1412.441</v>
       </c>
       <c r="F80">
-        <v>1464.762</v>
+        <v>1483.541</v>
       </c>
       <c r="G80">
         <v>273</v>
@@ -7847,37 +7847,37 @@
         <v>126</v>
       </c>
       <c r="M80">
-        <v>345.3908796</v>
+        <v>349.8189678</v>
       </c>
       <c r="N80">
-        <v>-219.3908796</v>
+        <v>-223.8189678</v>
       </c>
       <c r="O80">
-        <v>-37.296449532</v>
+        <v>-38.049224526</v>
       </c>
       <c r="P80">
-        <v>-182.094430068</v>
+        <v>-185.769743274</v>
       </c>
       <c r="Q80">
-        <v>-168.494430068</v>
+        <v>-172.169743274</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1472165945058039</v>
+        <v>0.1520459561489374</v>
       </c>
       <c r="T80">
-        <v>2.342184630619027</v>
+        <v>2.453717232077076</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06201669257974234</v>
+        <v>0.06123167115468232</v>
       </c>
       <c r="W80">
-        <v>0.2211764638896968</v>
+        <v>0.2213615719417259</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3648040739984844</v>
+        <v>0.3601863009098959</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2068052926252403</v>
+        <v>0.2087052926252403</v>
       </c>
       <c r="C81">
-        <v>-727.9892360052638</v>
+        <v>-751.3761930127721</v>
       </c>
       <c r="D81">
-        <v>482.5517639947361</v>
+        <v>477.9438069872278</v>
       </c>
       <c r="E81">
-        <v>1412.441</v>
+        <v>1431.22</v>
       </c>
       <c r="F81">
-        <v>1483.541</v>
+        <v>1502.32</v>
       </c>
       <c r="G81">
         <v>273</v>
@@ -7929,37 +7929,37 @@
         <v>126</v>
       </c>
       <c r="M81">
-        <v>349.8189678</v>
+        <v>354.247056</v>
       </c>
       <c r="N81">
-        <v>-223.8189678</v>
+        <v>-228.247056</v>
       </c>
       <c r="O81">
-        <v>-38.049224526</v>
+        <v>-38.80199952</v>
       </c>
       <c r="P81">
-        <v>-185.769743274</v>
+        <v>-189.44505648</v>
       </c>
       <c r="Q81">
-        <v>-172.169743274</v>
+        <v>-175.84505648</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1520459561489374</v>
+        <v>0.1573582539563843</v>
       </c>
       <c r="T81">
-        <v>2.453717232077076</v>
+        <v>2.576403093680929</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06123167115468232</v>
+        <v>0.06046627526524879</v>
       </c>
       <c r="W81">
-        <v>0.2213615719417259</v>
+        <v>0.2215420522924543</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3601863009098959</v>
+        <v>0.3556839721485222</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2087052926252403</v>
+        <v>0.2106052926252403</v>
       </c>
       <c r="C82">
-        <v>-751.3761930127721</v>
+        <v>-774.6759783315397</v>
       </c>
       <c r="D82">
-        <v>477.9438069872278</v>
+        <v>473.4230216684603</v>
       </c>
       <c r="E82">
-        <v>1431.22</v>
+        <v>1449.999</v>
       </c>
       <c r="F82">
-        <v>1502.32</v>
+        <v>1521.099</v>
       </c>
       <c r="G82">
         <v>273</v>
@@ -8011,37 +8011,37 @@
         <v>126</v>
       </c>
       <c r="M82">
-        <v>354.247056</v>
+        <v>358.6751442</v>
       </c>
       <c r="N82">
-        <v>-228.247056</v>
+        <v>-232.6751442</v>
       </c>
       <c r="O82">
-        <v>-38.80199952</v>
+        <v>-39.554774514</v>
       </c>
       <c r="P82">
-        <v>-189.44505648</v>
+        <v>-193.120369686</v>
       </c>
       <c r="Q82">
-        <v>-175.84505648</v>
+        <v>-179.520369686</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1573582539563843</v>
+        <v>0.1632297410067203</v>
       </c>
       <c r="T82">
-        <v>2.576403093680929</v>
+        <v>2.712003256506242</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06046627526524879</v>
+        <v>0.05971977803975189</v>
       </c>
       <c r="W82">
-        <v>0.2215420522924543</v>
+        <v>0.2217180763382265</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3556839721485222</v>
+        <v>0.3512928119985406</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2106052926252403</v>
+        <v>0.2125052926252403</v>
       </c>
       <c r="C83">
-        <v>-774.6759783315397</v>
+        <v>-797.891042407653</v>
       </c>
       <c r="D83">
-        <v>473.4230216684603</v>
+        <v>468.986957592347</v>
       </c>
       <c r="E83">
-        <v>1449.999</v>
+        <v>1468.778</v>
       </c>
       <c r="F83">
-        <v>1521.099</v>
+        <v>1539.878</v>
       </c>
       <c r="G83">
         <v>273</v>
@@ -8093,37 +8093,37 @@
         <v>126</v>
       </c>
       <c r="M83">
-        <v>358.6751442</v>
+        <v>363.1032324</v>
       </c>
       <c r="N83">
-        <v>-232.6751442</v>
+        <v>-237.1032324</v>
       </c>
       <c r="O83">
-        <v>-39.554774514</v>
+        <v>-40.30754950800001</v>
       </c>
       <c r="P83">
-        <v>-193.120369686</v>
+        <v>-196.795682892</v>
       </c>
       <c r="Q83">
-        <v>-179.520369686</v>
+        <v>-183.195682892</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1632297410067203</v>
+        <v>0.1697536155070936</v>
       </c>
       <c r="T83">
-        <v>2.712003256506242</v>
+        <v>2.862670104089922</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05971977803975189</v>
+        <v>0.05899148806365734</v>
       </c>
       <c r="W83">
-        <v>0.2217180763382265</v>
+        <v>0.2218898071145896</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3512928119985406</v>
+        <v>0.3470087533156314</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2125052926252403</v>
+        <v>0.2144052926252403</v>
       </c>
       <c r="C84">
-        <v>-797.891042407653</v>
+        <v>-821.0237446952206</v>
       </c>
       <c r="D84">
-        <v>468.986957592347</v>
+        <v>464.6332553047793</v>
       </c>
       <c r="E84">
-        <v>1468.778</v>
+        <v>1487.557</v>
       </c>
       <c r="F84">
-        <v>1539.878</v>
+        <v>1558.657</v>
       </c>
       <c r="G84">
         <v>273</v>
@@ -8175,37 +8175,37 @@
         <v>126</v>
       </c>
       <c r="M84">
-        <v>363.1032324</v>
+        <v>367.5313206</v>
       </c>
       <c r="N84">
-        <v>-237.1032324</v>
+        <v>-241.5313206</v>
       </c>
       <c r="O84">
-        <v>-40.30754950800001</v>
+        <v>-41.06032450200001</v>
       </c>
       <c r="P84">
-        <v>-196.795682892</v>
+        <v>-200.470996098</v>
       </c>
       <c r="Q84">
-        <v>-183.195682892</v>
+        <v>-186.870996098</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1697536155070936</v>
+        <v>0.1770450046545697</v>
       </c>
       <c r="T84">
-        <v>2.862670104089922</v>
+        <v>3.031062463154035</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05899148806365734</v>
+        <v>0.05828074724361329</v>
       </c>
       <c r="W84">
-        <v>0.2218898071145896</v>
+        <v>0.222057399799956</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3470087533156314</v>
+        <v>0.3428279249624311</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2144052926252403</v>
+        <v>0.2163052926252403</v>
       </c>
       <c r="C85">
-        <v>-821.0237446952206</v>
+        <v>-844.0763578410124</v>
       </c>
       <c r="D85">
-        <v>464.6332553047793</v>
+        <v>460.3596421589878</v>
       </c>
       <c r="E85">
-        <v>1487.557</v>
+        <v>1506.336</v>
       </c>
       <c r="F85">
-        <v>1558.657</v>
+        <v>1577.436</v>
       </c>
       <c r="G85">
         <v>273</v>
@@ -8257,37 +8257,37 @@
         <v>126</v>
       </c>
       <c r="M85">
-        <v>367.5313206</v>
+        <v>371.9594088000001</v>
       </c>
       <c r="N85">
-        <v>-241.5313206</v>
+        <v>-245.9594088000001</v>
       </c>
       <c r="O85">
-        <v>-41.06032450200001</v>
+        <v>-41.81309949600001</v>
       </c>
       <c r="P85">
-        <v>-200.470996098</v>
+        <v>-204.1463093040001</v>
       </c>
       <c r="Q85">
-        <v>-186.870996098</v>
+        <v>-190.5463093040001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1770450046545697</v>
+        <v>0.1852478174454804</v>
       </c>
       <c r="T85">
-        <v>3.031062463154035</v>
+        <v>3.220503867101163</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05828074724361329</v>
+        <v>0.05758692882404645</v>
       </c>
       <c r="W85">
-        <v>0.222057399799956</v>
+        <v>0.2222210021832899</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3428279249624311</v>
+        <v>0.3387466401414497</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2163052926252403</v>
+        <v>0.2182052926252403</v>
       </c>
       <c r="C86">
-        <v>-844.0763578410122</v>
+        <v>-867.0510716402655</v>
       </c>
       <c r="D86">
-        <v>460.3596421589878</v>
+        <v>456.1639283597345</v>
       </c>
       <c r="E86">
-        <v>1506.336</v>
+        <v>1525.115</v>
       </c>
       <c r="F86">
-        <v>1577.436</v>
+        <v>1596.215</v>
       </c>
       <c r="G86">
         <v>273</v>
@@ -8339,37 +8339,37 @@
         <v>126</v>
       </c>
       <c r="M86">
-        <v>371.9594088</v>
+        <v>376.387497</v>
       </c>
       <c r="N86">
-        <v>-245.9594088</v>
+        <v>-250.387497</v>
       </c>
       <c r="O86">
-        <v>-41.81309949600001</v>
+        <v>-42.56587449000001</v>
       </c>
       <c r="P86">
-        <v>-204.146309304</v>
+        <v>-207.82162251</v>
       </c>
       <c r="Q86">
-        <v>-190.546309304</v>
+        <v>-194.22162251</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1852478174454803</v>
+        <v>0.1945443386085123</v>
       </c>
       <c r="T86">
-        <v>3.220503867101161</v>
+        <v>3.435204124907905</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05758692882404646</v>
+        <v>0.05690943554376356</v>
       </c>
       <c r="W86">
-        <v>0.2222210021832899</v>
+        <v>0.2223807550987806</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3387466401414497</v>
+        <v>0.3347613855515503</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2182052926252403</v>
+        <v>0.2201052926252403</v>
       </c>
       <c r="C87">
-        <v>-867.0510716402655</v>
+        <v>-889.9499967781262</v>
       </c>
       <c r="D87">
-        <v>456.1639283597345</v>
+        <v>452.0440032218738</v>
       </c>
       <c r="E87">
-        <v>1525.115</v>
+        <v>1543.894</v>
       </c>
       <c r="F87">
-        <v>1596.215</v>
+        <v>1614.994</v>
       </c>
       <c r="G87">
         <v>273</v>
@@ -8421,37 +8421,37 @@
         <v>126</v>
       </c>
       <c r="M87">
-        <v>376.387497</v>
+        <v>380.8155852</v>
       </c>
       <c r="N87">
-        <v>-250.387497</v>
+        <v>-254.8155852</v>
       </c>
       <c r="O87">
-        <v>-42.56587449000001</v>
+        <v>-43.318649484</v>
       </c>
       <c r="P87">
-        <v>-207.82162251</v>
+        <v>-211.496935716</v>
       </c>
       <c r="Q87">
-        <v>-194.22162251</v>
+        <v>-197.896935716</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1945443386085123</v>
+        <v>0.205168934223406</v>
       </c>
       <c r="T87">
-        <v>3.435204124907905</v>
+        <v>3.680575848115613</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05690943554376356</v>
+        <v>0.05624769792116166</v>
       </c>
       <c r="W87">
-        <v>0.2223807550987806</v>
+        <v>0.2225367928301901</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3347613855515503</v>
+        <v>0.3308688113009509</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2201052926252403</v>
+        <v>0.2220052926252403</v>
       </c>
       <c r="C88">
-        <v>-889.9499967781262</v>
+        <v>-912.7751683701587</v>
       </c>
       <c r="D88">
-        <v>452.0440032218738</v>
+        <v>447.9978316298412</v>
       </c>
       <c r="E88">
-        <v>1543.894</v>
+        <v>1562.673</v>
       </c>
       <c r="F88">
-        <v>1614.994</v>
+        <v>1633.773</v>
       </c>
       <c r="G88">
         <v>273</v>
@@ -8503,37 +8503,37 @@
         <v>126</v>
       </c>
       <c r="M88">
-        <v>380.8155852</v>
+        <v>385.2436734</v>
       </c>
       <c r="N88">
-        <v>-254.8155852</v>
+        <v>-259.2436734</v>
       </c>
       <c r="O88">
-        <v>-43.318649484</v>
+        <v>-44.071424478</v>
       </c>
       <c r="P88">
-        <v>-211.496935716</v>
+        <v>-215.172248922</v>
       </c>
       <c r="Q88">
-        <v>-197.896935716</v>
+        <v>-201.572248922</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.205168934223406</v>
+        <v>0.2174280830098219</v>
       </c>
       <c r="T88">
-        <v>3.680575848115613</v>
+        <v>3.963697067201429</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05624769792116166</v>
+        <v>0.05560117265770004</v>
       </c>
       <c r="W88">
-        <v>0.2225367928301901</v>
+        <v>0.2226892434873143</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3308688113009509</v>
+        <v>0.3270657215158825</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2220052926252403</v>
+        <v>0.2239052926252403</v>
       </c>
       <c r="C89">
-        <v>-912.7751683701587</v>
+        <v>-935.5285493143929</v>
       </c>
       <c r="D89">
-        <v>447.9978316298412</v>
+        <v>444.0234506856071</v>
       </c>
       <c r="E89">
-        <v>1562.673</v>
+        <v>1581.452</v>
       </c>
       <c r="F89">
-        <v>1633.773</v>
+        <v>1652.552</v>
       </c>
       <c r="G89">
         <v>273</v>
@@ -8585,37 +8585,37 @@
         <v>126</v>
       </c>
       <c r="M89">
-        <v>385.2436734</v>
+        <v>389.6717616</v>
       </c>
       <c r="N89">
-        <v>-259.2436734</v>
+        <v>-263.6717616</v>
       </c>
       <c r="O89">
-        <v>-44.071424478</v>
+        <v>-44.824199472</v>
       </c>
       <c r="P89">
-        <v>-215.172248922</v>
+        <v>-218.847562128</v>
       </c>
       <c r="Q89">
-        <v>-201.572248922</v>
+        <v>-205.247562128</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2174280830098219</v>
+        <v>0.2317304232606404</v>
       </c>
       <c r="T89">
-        <v>3.963697067201429</v>
+        <v>4.294005156134882</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05560117265770004</v>
+        <v>0.05496934115022618</v>
       </c>
       <c r="W89">
-        <v>0.2226892434873143</v>
+        <v>0.2228382293567767</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3270657215158825</v>
+        <v>0.3233490655895657</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2239052926252403</v>
+        <v>0.2258052926252403</v>
       </c>
       <c r="C90">
-        <v>-935.5285493143929</v>
+        <v>-958.2120334665215</v>
       </c>
       <c r="D90">
-        <v>444.0234506856071</v>
+        <v>440.1189665334785</v>
       </c>
       <c r="E90">
-        <v>1581.452</v>
+        <v>1600.231</v>
       </c>
       <c r="F90">
-        <v>1652.552</v>
+        <v>1671.331</v>
       </c>
       <c r="G90">
         <v>273</v>
@@ -8667,37 +8667,37 @@
         <v>126</v>
       </c>
       <c r="M90">
-        <v>389.6717616</v>
+        <v>394.0998498</v>
       </c>
       <c r="N90">
-        <v>-263.6717616</v>
+        <v>-268.0998498</v>
       </c>
       <c r="O90">
-        <v>-44.824199472</v>
+        <v>-45.576974466</v>
       </c>
       <c r="P90">
-        <v>-218.847562128</v>
+        <v>-222.522875334</v>
       </c>
       <c r="Q90">
-        <v>-205.247562128</v>
+        <v>-208.922875334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2317304232606404</v>
+        <v>0.2486331890116077</v>
       </c>
       <c r="T90">
-        <v>4.294005156134882</v>
+        <v>4.684369261238053</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05496934115022618</v>
+        <v>0.05435170810359441</v>
       </c>
       <c r="W90">
-        <v>0.2228382293567767</v>
+        <v>0.2229838672291724</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3233490655895657</v>
+        <v>0.3197159300211436</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2258052926252403</v>
+        <v>0.2277052926252403</v>
       </c>
       <c r="C91">
-        <v>-958.2120334665215</v>
+        <v>-980.8274486490296</v>
       </c>
       <c r="D91">
-        <v>440.1189665334785</v>
+        <v>436.2825513509703</v>
       </c>
       <c r="E91">
-        <v>1600.231</v>
+        <v>1619.01</v>
       </c>
       <c r="F91">
-        <v>1671.331</v>
+        <v>1690.11</v>
       </c>
       <c r="G91">
         <v>273</v>
@@ -8749,37 +8749,37 @@
         <v>126</v>
       </c>
       <c r="M91">
-        <v>394.0998498</v>
+        <v>398.527938</v>
       </c>
       <c r="N91">
-        <v>-268.0998498</v>
+        <v>-272.527938</v>
       </c>
       <c r="O91">
-        <v>-45.576974466</v>
+        <v>-46.32974946</v>
       </c>
       <c r="P91">
-        <v>-222.522875334</v>
+        <v>-226.19818854</v>
       </c>
       <c r="Q91">
-        <v>-208.922875334</v>
+        <v>-212.59818854</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2486331890116077</v>
+        <v>0.2689165079127685</v>
       </c>
       <c r="T91">
-        <v>4.684369261238053</v>
+        <v>5.152806187361858</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05435170810359441</v>
+        <v>0.0537478002357767</v>
       </c>
       <c r="W91">
-        <v>0.2229838672291724</v>
+        <v>0.2231262687044039</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3197159300211436</v>
+        <v>0.3161635307986864</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2277052926252403</v>
+        <v>0.2296052926252403</v>
       </c>
       <c r="C92">
-        <v>-980.8274486490296</v>
+        <v>-1003.376559504308</v>
       </c>
       <c r="D92">
-        <v>436.2825513509703</v>
+        <v>432.5124404956923</v>
       </c>
       <c r="E92">
-        <v>1619.01</v>
+        <v>1637.789</v>
       </c>
       <c r="F92">
-        <v>1690.11</v>
+        <v>1708.889</v>
       </c>
       <c r="G92">
         <v>273</v>
@@ -8831,37 +8831,37 @@
         <v>126</v>
       </c>
       <c r="M92">
-        <v>398.527938</v>
+        <v>402.9560262</v>
       </c>
       <c r="N92">
-        <v>-272.527938</v>
+        <v>-276.9560262</v>
       </c>
       <c r="O92">
-        <v>-46.32974946</v>
+        <v>-47.082524454</v>
       </c>
       <c r="P92">
-        <v>-226.19818854</v>
+        <v>-229.873501746</v>
       </c>
       <c r="Q92">
-        <v>-212.59818854</v>
+        <v>-216.273501746</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2689165079127685</v>
+        <v>0.2937072310141873</v>
       </c>
       <c r="T92">
-        <v>5.152806187361858</v>
+        <v>5.725340208179844</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0537478002357767</v>
+        <v>0.05315716506835058</v>
       </c>
       <c r="W92">
-        <v>0.2231262687044039</v>
+        <v>0.223265540476883</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3161635307986864</v>
+        <v>0.3126892062844152</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2296052926252403</v>
+        <v>0.2315052926252403</v>
       </c>
       <c r="C93">
-        <v>-1003.376559504308</v>
+        <v>-1025.861070201096</v>
       </c>
       <c r="D93">
-        <v>432.5124404956923</v>
+        <v>428.8069297989043</v>
       </c>
       <c r="E93">
-        <v>1637.789</v>
+        <v>1656.568</v>
       </c>
       <c r="F93">
-        <v>1708.889</v>
+        <v>1727.668</v>
       </c>
       <c r="G93">
         <v>273</v>
@@ -8913,37 +8913,37 @@
         <v>126</v>
       </c>
       <c r="M93">
-        <v>402.9560262</v>
+        <v>407.3841144</v>
       </c>
       <c r="N93">
-        <v>-276.9560262</v>
+        <v>-281.3841144</v>
       </c>
       <c r="O93">
-        <v>-47.082524454</v>
+        <v>-47.835299448</v>
       </c>
       <c r="P93">
-        <v>-229.873501746</v>
+        <v>-233.548814952</v>
       </c>
       <c r="Q93">
-        <v>-216.273501746</v>
+        <v>-219.948814952</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2937072310141873</v>
+        <v>0.3246956348909608</v>
       </c>
       <c r="T93">
-        <v>5.725340208179844</v>
+        <v>6.441007734202326</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05315716506835058</v>
+        <v>0.05257936979586852</v>
       </c>
       <c r="W93">
-        <v>0.223265540476883</v>
+        <v>0.2234017846021342</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3126892062844152</v>
+        <v>0.3092904105639324</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2315052926252403</v>
+        <v>0.2334052926252403</v>
       </c>
       <c r="C94">
-        <v>-1025.861070201096</v>
+        <v>-1048.282627002995</v>
       </c>
       <c r="D94">
-        <v>428.8069297989043</v>
+        <v>425.1643729970048</v>
       </c>
       <c r="E94">
-        <v>1656.568</v>
+        <v>1675.347</v>
       </c>
       <c r="F94">
-        <v>1727.668</v>
+        <v>1746.447</v>
       </c>
       <c r="G94">
         <v>273</v>
@@ -8995,37 +8995,37 @@
         <v>126</v>
       </c>
       <c r="M94">
-        <v>407.3841144</v>
+        <v>411.8122026</v>
       </c>
       <c r="N94">
-        <v>-281.3841144</v>
+        <v>-285.8122026</v>
       </c>
       <c r="O94">
-        <v>-47.835299448</v>
+        <v>-48.588074442</v>
       </c>
       <c r="P94">
-        <v>-233.548814952</v>
+        <v>-237.224128158</v>
       </c>
       <c r="Q94">
-        <v>-219.948814952</v>
+        <v>-223.624128158</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3246956348909608</v>
+        <v>0.3645378684468123</v>
       </c>
       <c r="T94">
-        <v>6.441007734202326</v>
+        <v>7.36115169623123</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05257936979586852</v>
+        <v>0.052014000228171</v>
       </c>
       <c r="W94">
-        <v>0.2234017846021342</v>
+        <v>0.2235350987461973</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3092904105639324</v>
+        <v>0.3059647072245353</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2334052926252403</v>
+        <v>0.2353052926252403</v>
       </c>
       <c r="C95">
-        <v>-1048.282627002995</v>
+        <v>-1070.642820707164</v>
       </c>
       <c r="D95">
-        <v>425.1643729970048</v>
+        <v>421.5831792928364</v>
       </c>
       <c r="E95">
-        <v>1675.347</v>
+        <v>1694.126</v>
       </c>
       <c r="F95">
-        <v>1746.447</v>
+        <v>1765.226</v>
       </c>
       <c r="G95">
         <v>273</v>
@@ -9077,37 +9077,37 @@
         <v>126</v>
       </c>
       <c r="M95">
-        <v>411.8122026</v>
+        <v>416.2402908</v>
       </c>
       <c r="N95">
-        <v>-285.8122026</v>
+        <v>-290.2402908</v>
       </c>
       <c r="O95">
-        <v>-48.588074442</v>
+        <v>-49.340849436</v>
       </c>
       <c r="P95">
-        <v>-237.224128158</v>
+        <v>-240.899441364</v>
       </c>
       <c r="Q95">
-        <v>-223.624128158</v>
+        <v>-227.299441364</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3645378684468123</v>
+        <v>0.4176608465212812</v>
       </c>
       <c r="T95">
-        <v>7.36115169623123</v>
+        <v>8.588010312269772</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.052014000228171</v>
+        <v>0.05146065980021174</v>
       </c>
       <c r="W95">
-        <v>0.2235350987461973</v>
+        <v>0.2236655764191101</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3059647072245353</v>
+        <v>0.3027097635306573</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2353052926252403</v>
+        <v>0.2372052926252403</v>
       </c>
       <c r="C96">
-        <v>-1070.642820707164</v>
+        <v>-1092.943188960795</v>
       </c>
       <c r="D96">
-        <v>421.5831792928364</v>
+        <v>418.061811039205</v>
       </c>
       <c r="E96">
-        <v>1694.126</v>
+        <v>1712.905</v>
       </c>
       <c r="F96">
-        <v>1765.226</v>
+        <v>1784.005</v>
       </c>
       <c r="G96">
         <v>273</v>
@@ -9159,37 +9159,37 @@
         <v>126</v>
       </c>
       <c r="M96">
-        <v>416.2402908</v>
+        <v>420.668379</v>
       </c>
       <c r="N96">
-        <v>-290.2402908</v>
+        <v>-294.668379</v>
       </c>
       <c r="O96">
-        <v>-49.340849436</v>
+        <v>-50.09362443000001</v>
       </c>
       <c r="P96">
-        <v>-240.899441364</v>
+        <v>-244.57475457</v>
       </c>
       <c r="Q96">
-        <v>-227.299441364</v>
+        <v>-230.97475457</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4176608465212812</v>
+        <v>0.4920330158255376</v>
       </c>
       <c r="T96">
-        <v>8.588010312269772</v>
+        <v>10.30561237472373</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05146065980021174</v>
+        <v>0.05091896864442003</v>
       </c>
       <c r="W96">
-        <v>0.2236655764191101</v>
+        <v>0.2237933071936458</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3027097635306573</v>
+        <v>0.2995233449671766</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2372052926252403</v>
+        <v>0.2391052926252404</v>
       </c>
       <c r="C97">
-        <v>-1092.943188960795</v>
+        <v>-1115.185218462469</v>
       </c>
       <c r="D97">
-        <v>418.061811039205</v>
+        <v>414.5987815375312</v>
       </c>
       <c r="E97">
-        <v>1712.905</v>
+        <v>1731.684</v>
       </c>
       <c r="F97">
-        <v>1784.005</v>
+        <v>1802.784</v>
       </c>
       <c r="G97">
         <v>273</v>
@@ -9241,37 +9241,37 @@
         <v>126</v>
       </c>
       <c r="M97">
-        <v>420.668379</v>
+        <v>425.0964672000001</v>
       </c>
       <c r="N97">
-        <v>-294.668379</v>
+        <v>-299.0964672000001</v>
       </c>
       <c r="O97">
-        <v>-50.09362443000001</v>
+        <v>-50.84639942400001</v>
       </c>
       <c r="P97">
-        <v>-244.57475457</v>
+        <v>-248.250067776</v>
       </c>
       <c r="Q97">
-        <v>-230.97475457</v>
+        <v>-234.650067776</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4920330158255376</v>
+        <v>0.6035912697819221</v>
       </c>
       <c r="T97">
-        <v>10.30561237472373</v>
+        <v>12.88201546840467</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05091896864442003</v>
+        <v>0.05038856272104064</v>
       </c>
       <c r="W97">
-        <v>0.2237933071936458</v>
+        <v>0.2239183769103786</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2995233449671766</v>
+        <v>0.2964033101237685</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2391052926252403</v>
+        <v>0.2410052926252403</v>
       </c>
       <c r="C98">
-        <v>-1115.185218462469</v>
+        <v>-1137.370347054986</v>
       </c>
       <c r="D98">
-        <v>414.5987815375314</v>
+        <v>411.1926529450143</v>
       </c>
       <c r="E98">
-        <v>1731.684</v>
+        <v>1750.463</v>
       </c>
       <c r="F98">
-        <v>1802.784</v>
+        <v>1821.563</v>
       </c>
       <c r="G98">
         <v>273</v>
@@ -9323,37 +9323,37 @@
         <v>126</v>
       </c>
       <c r="M98">
-        <v>425.0964672</v>
+        <v>429.5245554</v>
       </c>
       <c r="N98">
-        <v>-299.0964672</v>
+        <v>-303.5245554</v>
       </c>
       <c r="O98">
-        <v>-50.846399424</v>
+        <v>-51.599174418</v>
       </c>
       <c r="P98">
-        <v>-248.250067776</v>
+        <v>-251.925380982</v>
       </c>
       <c r="Q98">
-        <v>-234.650067776</v>
+        <v>-238.325380982</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6035912697819207</v>
+        <v>0.789521693042561</v>
       </c>
       <c r="T98">
-        <v>12.88201546840464</v>
+        <v>17.17602062453951</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05038856272104066</v>
+        <v>0.04986909300226704</v>
       </c>
       <c r="W98">
-        <v>0.2239183769103786</v>
+        <v>0.2240408678700654</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2964033101237685</v>
+        <v>0.2933476058956884</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2410052926252403</v>
+        <v>0.2429052926252404</v>
       </c>
       <c r="C99">
-        <v>-1137.370347054986</v>
+        <v>-1159.499965715884</v>
       </c>
       <c r="D99">
-        <v>411.1926529450143</v>
+        <v>407.842034284116</v>
       </c>
       <c r="E99">
-        <v>1750.463</v>
+        <v>1769.242</v>
       </c>
       <c r="F99">
-        <v>1821.563</v>
+        <v>1840.342</v>
       </c>
       <c r="G99">
         <v>273</v>
@@ -9405,37 +9405,37 @@
         <v>126</v>
       </c>
       <c r="M99">
-        <v>429.5245554</v>
+        <v>433.9526436</v>
       </c>
       <c r="N99">
-        <v>-303.5245554</v>
+        <v>-307.9526436</v>
       </c>
       <c r="O99">
-        <v>-51.599174418</v>
+        <v>-52.351949412</v>
       </c>
       <c r="P99">
-        <v>-251.925380982</v>
+        <v>-255.600694188</v>
       </c>
       <c r="Q99">
-        <v>-238.325380982</v>
+        <v>-242.000694188</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.789521693042561</v>
+        <v>1.161382539563842</v>
       </c>
       <c r="T99">
-        <v>17.17602062453951</v>
+        <v>25.76403093680927</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04986909300226704</v>
+        <v>0.04936022470632554</v>
       </c>
       <c r="W99">
-        <v>0.2240408678700654</v>
+        <v>0.2241608590142485</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2933476058956884</v>
+        <v>0.2903542629783855</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2429052926252404</v>
+        <v>0.2448052926252403</v>
       </c>
       <c r="C100">
-        <v>-1159.499965715884</v>
+        <v>-1181.575420451423</v>
       </c>
       <c r="D100">
-        <v>407.842034284116</v>
+        <v>404.5455795485766</v>
       </c>
       <c r="E100">
-        <v>1769.242</v>
+        <v>1788.021</v>
       </c>
       <c r="F100">
-        <v>1840.342</v>
+        <v>1859.121</v>
       </c>
       <c r="G100">
         <v>273</v>
@@ -9487,37 +9487,37 @@
         <v>126</v>
       </c>
       <c r="M100">
-        <v>433.9526436</v>
+        <v>438.3807318</v>
       </c>
       <c r="N100">
-        <v>-307.9526436</v>
+        <v>-312.3807318</v>
       </c>
       <c r="O100">
-        <v>-52.351949412</v>
+        <v>-53.104724406</v>
       </c>
       <c r="P100">
-        <v>-255.600694188</v>
+        <v>-259.276007394</v>
       </c>
       <c r="Q100">
-        <v>-242.000694188</v>
+        <v>-245.676007394</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.161382539563842</v>
+        <v>2.276965079127683</v>
       </c>
       <c r="T100">
-        <v>25.76403093680927</v>
+        <v>51.52806187361854</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04936022470632554</v>
+        <v>0.04886163657797882</v>
       </c>
       <c r="W100">
-        <v>0.2241608590142485</v>
+        <v>0.2242784260949126</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2903542629783855</v>
+        <v>0.2874213916351696</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2448052926252403</v>
-      </c>
-      <c r="C101">
-        <v>-1181.575420451423</v>
-      </c>
-      <c r="D101">
-        <v>404.5455795485766</v>
-      </c>
-      <c r="E101">
-        <v>1788.021</v>
-      </c>
-      <c r="F101">
-        <v>1859.121</v>
-      </c>
-      <c r="G101">
-        <v>273</v>
-      </c>
-      <c r="H101">
-        <v>1806.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>139.6</v>
-      </c>
-      <c r="K101">
-        <v>13.59999999999999</v>
-      </c>
-      <c r="L101">
-        <v>126</v>
-      </c>
-      <c r="M101">
-        <v>438.3807318</v>
-      </c>
-      <c r="N101">
-        <v>-312.3807318</v>
-      </c>
-      <c r="O101">
-        <v>-53.104724406</v>
-      </c>
-      <c r="P101">
-        <v>-259.276007394</v>
-      </c>
-      <c r="Q101">
-        <v>-245.676007394</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.276965079127683</v>
-      </c>
-      <c r="T101">
-        <v>51.52806187361854</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04886163657797882</v>
-      </c>
-      <c r="W101">
-        <v>0.2242784260949126</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2874213916351696</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
